--- a/fase_2/precios/lista_tomo2.xlsx
+++ b/fase_2/precios/lista_tomo2.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,12 +20,2139 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="711">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
   <si>
     <t xml:space="preserve">precio_venta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127-746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127-747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127-748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">914-161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">914-162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127-745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">934-103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119-548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">934-104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122-929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-830</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130-276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123-083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130-275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130-224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">934-820</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123-027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123-028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127-131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130-244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-190</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123-492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131-100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131-102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114-932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-810</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127-115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942-764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135-049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131-079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">935-046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-720</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">927-058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942-774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131-091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131-093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131-094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">919-235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130-235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130-238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942-769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">927-059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128-159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-710</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942-759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127-065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130-229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139-071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122-982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131-086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">931-066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135-047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135-048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942-772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-830</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">935-199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135-243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110-967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">943-475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">960-561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141-091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">930-295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130-298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">931-146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942-749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">943-501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135-229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942-181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">914-859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">934-814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">938-215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">982-371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115-116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139-067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942-792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127-184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">938-165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-490</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139-062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135-246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">923-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">938-170</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">938-707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130-282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">934-815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119-365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">938-211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">935-197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">919-229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130-281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103-159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">096-916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107-937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103-539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-190</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942-183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">938-760</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942-761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141-093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">943-407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139-937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130-293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">927-179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139-069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">939-154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-770</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130-394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">922-994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942-751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">934-822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">938-161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130-338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139-966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">960-565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139-962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942-753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135-020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">943-476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107-017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">960-564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139-063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">935-194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">938-166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123-314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">934-809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">907-863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103-187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139-941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103-528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114-978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">910-793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127-069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">960-562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">938-295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942-967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942-756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">938-856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">938-242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">931-190</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942-797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">938-507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">919-342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139-031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139-032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942-970</t>
+  </si>
+  <si>
+    <t xml:space="preserve">943-063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">934-958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">919-228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139-068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942-794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139-064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">938-329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942-745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942-796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139-033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">931-230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131-231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139-963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">931-232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131-233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135-244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">934-806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">938-838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">938-840</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115-125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130-308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942-746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119-429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">923-223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">938-508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942-750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130-314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139-074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139-965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126-160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126-161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942-799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123-306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127-251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123-311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">935-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123-309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123-310</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127-252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">923-295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">923-296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123-297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128-169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135-305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135-307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139-026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135-014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">928-157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123-288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123-289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135-056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127-244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123-291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129-039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129-040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122-957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130-360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">927-066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135-315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">923-318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123-319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139-061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110-968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942-752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">934-236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119-472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">930-326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135-299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123-277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123-278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">934-823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128-154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">935-201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">938-749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139-065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115-182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130-317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">922-971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121-127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115-183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-920</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131-173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">938-310</t>
+  </si>
+  <si>
+    <t xml:space="preserve">934-194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127-287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">927-298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942-182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127-299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-260</t>
+  </si>
+  <si>
+    <t xml:space="preserve">938-704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">934-272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">931-209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">928-250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">938-829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">938-265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">927-859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">934-253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">938-830</t>
+  </si>
+  <si>
+    <t xml:space="preserve">931-187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">938-827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">938-266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">938-164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">938-263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942-180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">934-187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123-114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131-137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">931-138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103-173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107-911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114-985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">927-207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">943-028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">938-173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">927-064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">902-891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123-112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135-074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135-323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114-252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130-808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114-255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114-262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130-813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122-636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119-136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114-268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122-633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122-634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-550</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130-816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114-272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129-303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141-460</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141-462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141-463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141-461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141-458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141-459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">943-437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">943-438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">841-739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">943-441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">735-688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">943-436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">943-440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942-507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942-516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127-778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">943-369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942-515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130-828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942-512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130-179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">052-998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">938-487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942-509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-480</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942-518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">088-550</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130-807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114-530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119-774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113-020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106-195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130-195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130-805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122-808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110-346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122-824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128-143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110-441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">096-357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119-586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">940-646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119-597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110-440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110-445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-720</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122-789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-550</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115-764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119-764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110-443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131-058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122-788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122-799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128-147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131-057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">936-999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">941-271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">929-368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">937-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">910-432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">900-424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">921-318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">910-434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">921-980</t>
+  </si>
+  <si>
+    <t xml:space="preserve">932-386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">906-163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">921-891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">929-425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">929-426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">735-691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">735-692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">902-642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">926-054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132-034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">940-375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">941-205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">925-037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">973-253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130-843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130-844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128-152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122-832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119-593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131-056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">068-772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123-990</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123-991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110-660</t>
+  </si>
+  <si>
+    <t xml:space="preserve">075-032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">075-036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134-178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942-042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942-043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942-437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942-440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942-441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114-586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">096-514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">078-731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-470</t>
+  </si>
+  <si>
+    <t xml:space="preserve">078-732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111-113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107-321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107-322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115-770</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115-771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115-773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130-997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143-467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128-121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128-125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">841-725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136-669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126-732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">941-828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133-442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">841-724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">841-726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">933-265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135-651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">841-660</t>
+  </si>
+  <si>
+    <t xml:space="preserve">903-990</t>
+  </si>
+  <si>
+    <t xml:space="preserve">841-707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">933-432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135-701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135-702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135-703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113-296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">835-704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135-705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121-718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114-562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135-722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135-723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135-724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123-946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">841-829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133-434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">841-714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">835-659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135-661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121-722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118-851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114-561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118-846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">941-287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127-898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942-229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">935-989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942-378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942-379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128-211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123-936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123-943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128-209</t>
   </si>
 </sst>
 </file>
@@ -35,11 +2162,12 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -59,6 +2187,7 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
+      <color rgb="FFE2E2E2"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -67,11 +2196,6 @@
       <color rgb="FFFFFFFF"/>
       <name val="Inter"/>
       <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="DejaVu Sans Condensed"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -135,8 +2259,8 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -173,7 +2297,7 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF2A6099"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFE2E2E2"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -211,112 +2335,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
-  <a:themeElements>
-    <a:clrScheme name="LibreOffice">
-      <a:dk1>
-        <a:srgbClr val="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:srgbClr val="ffffff"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="000000"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="ffffff"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="18a303"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="0369a3"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="a33e03"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8e03a3"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="c99c00"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="c9211e"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000ee"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="551a8b"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme>
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -324,6 +2342,9 @@
   </sheetPr>
   <dimension ref="A1:B715"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.45"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -334,5712 +2355,5712 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
-        <v>138459</v>
+      <c r="A2" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>1340</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="n">
-        <v>142467</v>
+      <c r="A3" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>1120</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
-        <v>142468</v>
+      <c r="A4" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>1120</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="n">
-        <v>127746</v>
+      <c r="A5" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="B5" s="0" t="n">
         <v>2000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="n">
-        <v>127747</v>
+      <c r="A6" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="B6" s="0" t="n">
         <v>2000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="n">
-        <v>127748</v>
+      <c r="A7" s="3" t="s">
+        <v>7</v>
       </c>
       <c r="B7" s="0" t="n">
         <v>2000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="n">
-        <v>914161</v>
+      <c r="A8" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="B8" s="0" t="n">
         <v>2000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="n">
-        <v>914162</v>
+      <c r="A9" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="B9" s="0" t="n">
         <v>2000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="n">
-        <v>127745</v>
+      <c r="A10" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="B10" s="0" t="n">
         <v>2000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="n">
-        <v>142469</v>
+      <c r="A11" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="B11" s="0" t="n">
         <v>2000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="n">
-        <v>934103</v>
+      <c r="A12" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="B12" s="0" t="n">
         <v>1590</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="n">
-        <v>119548</v>
+      <c r="A13" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="B13" s="0" t="n">
         <v>1590</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="n">
-        <v>934104</v>
+      <c r="A14" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="B14" s="0" t="n">
         <v>1590</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="n">
-        <v>138457</v>
+      <c r="A15" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="B15" s="0" t="n">
         <v>1330</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="n">
-        <v>134102</v>
+      <c r="A16" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="B16" s="0" t="n">
         <v>1330</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="n">
-        <v>122929</v>
+      <c r="A17" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="B17" s="0" t="n">
         <v>1340</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="n">
-        <v>142823</v>
+      <c r="A18" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="B18" s="0" t="n">
         <v>3020</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="n">
-        <v>142830</v>
+      <c r="A19" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="B19" s="0" t="n">
         <v>3520</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="n">
-        <v>130276</v>
+      <c r="A20" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="B20" s="0" t="n">
         <v>3020</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="n">
-        <v>138184</v>
+      <c r="A21" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="B21" s="0" t="n">
         <v>3160</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="n">
-        <v>142809</v>
+      <c r="A22" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="B22" s="0" t="n">
         <v>3520</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="n">
-        <v>123083</v>
+      <c r="A23" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="B23" s="0" t="n">
         <v>2550</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="n">
-        <v>130275</v>
+      <c r="A24" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="B24" s="0" t="n">
         <v>3520</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="n">
-        <v>130224</v>
+      <c r="A25" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="B25" s="0" t="n">
         <v>2550</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="n">
-        <v>142817</v>
+      <c r="A26" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="B26" s="0" t="n">
         <v>2620</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="n">
-        <v>142818</v>
+      <c r="A27" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="B27" s="0" t="n">
         <v>2620</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="n">
-        <v>934820</v>
+      <c r="A28" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="B28" s="0" t="n">
         <v>1360</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="n">
-        <v>123027</v>
+      <c r="A29" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="B29" s="0" t="n">
         <v>3690</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="n">
-        <v>143079</v>
+      <c r="A30" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="B30" s="0" t="n">
         <v>1900</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="n">
-        <v>123028</v>
+      <c r="A31" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="B31" s="0" t="n">
         <v>2550</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3" t="n">
-        <v>127131</v>
+      <c r="A32" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="B32" s="0" t="n">
         <v>2550</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3" t="n">
-        <v>130244</v>
+      <c r="A33" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="B33" s="0" t="n">
         <v>2620</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="n">
-        <v>134215</v>
+      <c r="A34" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="B34" s="0" t="n">
         <v>2830</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3" t="n">
-        <v>138734</v>
+      <c r="A35" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="B35" s="0" t="n">
         <v>2830</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="3" t="n">
-        <v>134821</v>
+      <c r="A36" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="B36" s="0" t="n">
         <v>1360</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="3" t="n">
-        <v>138190</v>
+      <c r="A37" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="B37" s="0" t="n">
         <v>2800</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="3" t="n">
-        <v>123492</v>
+      <c r="A38" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="B38" s="0" t="n">
         <v>2620</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="3" t="n">
-        <v>134836</v>
+      <c r="A39" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="B39" s="0" t="n">
         <v>3160</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="3" t="n">
-        <v>138183</v>
+      <c r="A40" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="B40" s="0" t="n">
         <v>3760</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="3" t="n">
-        <v>138726</v>
+      <c r="A41" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="B41" s="0" t="n">
         <v>3460</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="3" t="n">
-        <v>142822</v>
+      <c r="A42" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="B42" s="0" t="n">
         <v>2620</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="3" t="n">
-        <v>131100</v>
+      <c r="A43" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="B43" s="0" t="n">
         <v>2860</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="3" t="n">
-        <v>131102</v>
+      <c r="A44" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="B44" s="0" t="n">
         <v>2930</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="3" t="n">
-        <v>138747</v>
+      <c r="A45" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="B45" s="0" t="n">
         <v>2930</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="3" t="n">
-        <v>114932</v>
+      <c r="A46" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="B46" s="0" t="n">
         <v>3090</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="3" t="n">
-        <v>142810</v>
+      <c r="A47" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="B47" s="0" t="n">
         <v>3520</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="3" t="n">
-        <v>143082</v>
+      <c r="A48" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="B48" s="0" t="n">
         <v>1130</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="3" t="n">
-        <v>127115</v>
+      <c r="A49" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="B49" s="0" t="n">
         <v>3020</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="3" t="n">
-        <v>138728</v>
+      <c r="A50" s="3" t="s">
+        <v>50</v>
       </c>
       <c r="B50" s="0" t="n">
         <v>3430</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="3" t="n">
-        <v>143083</v>
+      <c r="A51" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="B51" s="0" t="n">
         <v>1230</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="3" t="n">
-        <v>134204</v>
+      <c r="A52" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="B52" s="0" t="n">
         <v>2830</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="3" t="n">
-        <v>134205</v>
+      <c r="A53" s="3" t="s">
+        <v>53</v>
       </c>
       <c r="B53" s="0" t="n">
         <v>2830</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="3" t="n">
-        <v>138185</v>
+      <c r="A54" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="B54" s="0" t="n">
         <v>2830</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="3" t="n">
-        <v>942764</v>
+      <c r="A55" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="B55" s="0" t="n">
         <v>1090</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="3" t="n">
-        <v>135049</v>
+      <c r="A56" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="B56" s="0" t="n">
         <v>1620</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="3" t="n">
-        <v>138186</v>
+      <c r="A57" s="3" t="s">
+        <v>57</v>
       </c>
       <c r="B57" s="0" t="n">
         <v>2550</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="3" t="n">
-        <v>134210</v>
+      <c r="A58" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="B58" s="0" t="n">
         <v>2550</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="3" t="n">
-        <v>138188</v>
+      <c r="A59" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="B59" s="0" t="n">
         <v>2680</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="3" t="n">
-        <v>138189</v>
+      <c r="A60" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="B60" s="0" t="n">
         <v>2680</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="3" t="n">
-        <v>142824</v>
+      <c r="A61" s="3" t="s">
+        <v>61</v>
       </c>
       <c r="B61" s="0" t="n">
         <v>2890</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="3" t="n">
-        <v>142825</v>
+      <c r="A62" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="B62" s="0" t="n">
         <v>2890</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="3" t="n">
-        <v>143085</v>
+      <c r="A63" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="B63" s="0" t="n">
         <v>1200</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="3" t="n">
-        <v>134208</v>
+      <c r="A64" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="B64" s="0" t="n">
         <v>2510</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="3" t="n">
-        <v>143080</v>
+      <c r="A65" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="B65" s="0" t="n">
         <v>1480</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="3" t="n">
-        <v>131079</v>
+      <c r="A66" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="B66" s="0" t="n">
         <v>1480</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="3" t="n">
-        <v>138199</v>
+      <c r="A67" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="B67" s="0" t="n">
         <v>2830</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="3" t="n">
-        <v>142831</v>
+      <c r="A68" s="3" t="s">
+        <v>68</v>
       </c>
       <c r="B68" s="0" t="n">
         <v>3020</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="3" t="n">
-        <v>935046</v>
+      <c r="A69" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="B69" s="0" t="n">
         <v>1480</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="3" t="n">
-        <v>142864</v>
+      <c r="A70" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="B70" s="0" t="n">
         <v>2760</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="3" t="n">
-        <v>142876</v>
+      <c r="A71" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="B71" s="0" t="n">
         <v>3020</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="3" t="n">
-        <v>142865</v>
+      <c r="A72" s="3" t="s">
+        <v>72</v>
       </c>
       <c r="B72" s="0" t="n">
         <v>2760</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="3" t="n">
-        <v>138232</v>
+      <c r="A73" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="B73" s="0" t="n">
         <v>2760</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="3" t="n">
-        <v>138779</v>
+      <c r="A74" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="B74" s="0" t="n">
         <v>2760</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="3" t="n">
-        <v>138720</v>
+      <c r="A75" s="3" t="s">
+        <v>75</v>
       </c>
       <c r="B75" s="0" t="n">
         <v>3190</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="3" t="n">
-        <v>138721</v>
+      <c r="A76" s="3" t="s">
+        <v>76</v>
       </c>
       <c r="B76" s="0" t="n">
         <v>3190</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="3" t="n">
-        <v>138722</v>
+      <c r="A77" s="3" t="s">
+        <v>77</v>
       </c>
       <c r="B77" s="0" t="n">
         <v>2680</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="3" t="n">
-        <v>927058</v>
+      <c r="A78" s="3" t="s">
+        <v>78</v>
       </c>
       <c r="B78" s="0" t="n">
         <v>590</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="3" t="n">
-        <v>138724</v>
+      <c r="A79" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="B79" s="0" t="n">
         <v>2680</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="3" t="n">
-        <v>138725</v>
+      <c r="A80" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="B80" s="0" t="n">
         <v>3190</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="3" t="n">
-        <v>942774</v>
+      <c r="A81" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="B81" s="0" t="n">
         <v>660</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="3" t="n">
-        <v>138179</v>
+      <c r="A82" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="B82" s="0" t="n">
         <v>1940</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="3" t="n">
-        <v>138180</v>
+      <c r="A83" s="3" t="s">
+        <v>83</v>
       </c>
       <c r="B83" s="0" t="n">
         <v>2160</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="3" t="n">
-        <v>131091</v>
+      <c r="A84" s="3" t="s">
+        <v>84</v>
       </c>
       <c r="B84" s="0" t="n">
         <v>1620</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="3" t="n">
-        <v>131093</v>
+      <c r="A85" s="3" t="s">
+        <v>85</v>
       </c>
       <c r="B85" s="0" t="n">
         <v>1590</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="3" t="n">
-        <v>131094</v>
+      <c r="A86" s="3" t="s">
+        <v>86</v>
       </c>
       <c r="B86" s="0" t="n">
         <v>1760</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="3" t="n">
-        <v>919235</v>
+      <c r="A87" s="3" t="s">
+        <v>87</v>
       </c>
       <c r="B87" s="0" t="n">
         <v>660</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="3" t="n">
-        <v>130235</v>
+      <c r="A88" s="3" t="s">
+        <v>88</v>
       </c>
       <c r="B88" s="0" t="n">
         <v>1620</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="3" t="n">
-        <v>130238</v>
+      <c r="A89" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="B89" s="0" t="n">
         <v>1620</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="3" t="n">
-        <v>942769</v>
+      <c r="A90" s="3" t="s">
+        <v>90</v>
       </c>
       <c r="B90" s="0" t="n">
         <v>480</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="3" t="n">
-        <v>927059</v>
+      <c r="A91" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="B91" s="0" t="n">
         <v>660</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="3" t="n">
-        <v>138718</v>
+      <c r="A92" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="B92" s="0" t="n">
         <v>1940</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="3" t="n">
-        <v>128159</v>
+      <c r="A93" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="B93" s="0" t="n">
         <v>480</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="3" t="n">
-        <v>138181</v>
+      <c r="A94" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="B94" s="0" t="n">
         <v>1590</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="3" t="n">
-        <v>138182</v>
+      <c r="A95" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="B95" s="0" t="n">
         <v>1760</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="3" t="n">
-        <v>138710</v>
+      <c r="A96" s="3" t="s">
+        <v>96</v>
       </c>
       <c r="B96" s="0" t="n">
         <v>1590</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="3" t="n">
-        <v>138714</v>
+      <c r="A97" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="B97" s="0" t="n">
         <v>1590</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="3" t="n">
-        <v>138712</v>
+      <c r="A98" s="3" t="s">
+        <v>98</v>
       </c>
       <c r="B98" s="0" t="n">
         <v>1590</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="3" t="n">
-        <v>942759</v>
+      <c r="A99" s="3" t="s">
+        <v>99</v>
       </c>
       <c r="B99" s="0" t="n">
         <v>660</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="3" t="n">
-        <v>127065</v>
+      <c r="A100" s="3" t="s">
+        <v>100</v>
       </c>
       <c r="B100" s="0" t="n">
         <v>1410</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="3" t="n">
-        <v>130229</v>
+      <c r="A101" s="3" t="s">
+        <v>101</v>
       </c>
       <c r="B101" s="0" t="n">
         <v>1300</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="3" t="n">
-        <v>139071</v>
+      <c r="A102" s="3" t="s">
+        <v>102</v>
       </c>
       <c r="B102" s="0" t="n">
         <v>1590</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="3" t="n">
-        <v>122982</v>
+      <c r="A103" s="3" t="s">
+        <v>103</v>
       </c>
       <c r="B103" s="0" t="n">
         <v>1090</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="3" t="n">
-        <v>131086</v>
+      <c r="A104" s="3" t="s">
+        <v>104</v>
       </c>
       <c r="B104" s="0" t="n">
         <v>1690</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="3" t="n">
-        <v>138711</v>
+      <c r="A105" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="B105" s="0" t="n">
         <v>1590</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="3" t="n">
-        <v>131086</v>
+      <c r="A106" s="3" t="s">
+        <v>104</v>
       </c>
       <c r="B106" s="0" t="n">
         <v>1690</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="3" t="n">
-        <v>931066</v>
+      <c r="A107" s="3" t="s">
+        <v>106</v>
       </c>
       <c r="B107" s="0" t="n">
         <v>590</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="3" t="n">
-        <v>135047</v>
+      <c r="A108" s="3" t="s">
+        <v>107</v>
       </c>
       <c r="B108" s="0" t="n">
         <v>1690</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="3" t="n">
-        <v>135048</v>
+      <c r="A109" s="3" t="s">
+        <v>108</v>
       </c>
       <c r="B109" s="0" t="n">
         <v>1480</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="3" t="n">
-        <v>942772</v>
+      <c r="A110" s="3" t="s">
+        <v>109</v>
       </c>
       <c r="B110" s="0" t="n">
         <v>590</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="3" t="n">
-        <v>134830</v>
+      <c r="A111" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="B111" s="0" t="n">
         <v>1410</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="3" t="n">
-        <v>134198</v>
+      <c r="A112" s="3" t="s">
+        <v>111</v>
       </c>
       <c r="B112" s="0" t="n">
         <v>1690</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="3" t="n">
-        <v>935199</v>
+      <c r="A113" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="B113" s="0" t="n">
         <v>2550</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="3" t="n">
-        <v>134200</v>
+      <c r="A114" s="3" t="s">
+        <v>113</v>
       </c>
       <c r="B114" s="0" t="n">
         <v>2720</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="3" t="n">
-        <v>135243</v>
+      <c r="A115" s="3" t="s">
+        <v>114</v>
       </c>
       <c r="B115" s="0" t="n">
         <v>1200</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="3" t="n">
-        <v>110967</v>
+      <c r="A116" s="3" t="s">
+        <v>115</v>
       </c>
       <c r="B116" s="0" t="n">
         <v>660</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="3" t="n">
-        <v>943475</v>
+      <c r="A117" s="3" t="s">
+        <v>116</v>
       </c>
       <c r="B117" s="0" t="n">
         <v>910</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="3" t="n">
-        <v>138807</v>
+      <c r="A118" s="3" t="s">
+        <v>117</v>
       </c>
       <c r="B118" s="0" t="n">
         <v>3320</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="3" t="n">
-        <v>138808</v>
+      <c r="A119" s="3" t="s">
+        <v>118</v>
       </c>
       <c r="B119" s="0" t="n">
         <v>3320</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="3" t="n">
-        <v>960561</v>
+      <c r="A120" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="B120" s="0" t="n">
         <v>760</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="3" t="n">
-        <v>138793</v>
+      <c r="A121" s="3" t="s">
+        <v>120</v>
       </c>
       <c r="B121" s="0" t="n">
         <v>2510</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="3" t="n">
-        <v>142908</v>
+      <c r="A122" s="3" t="s">
+        <v>121</v>
       </c>
       <c r="B122" s="0" t="n">
         <v>2510</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="3" t="n">
-        <v>142762</v>
+      <c r="A123" s="3" t="s">
+        <v>122</v>
       </c>
       <c r="B123" s="0" t="n">
         <v>660</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="3" t="n">
-        <v>134222</v>
+      <c r="A124" s="3" t="s">
+        <v>123</v>
       </c>
       <c r="B124" s="0" t="n">
         <v>2240</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="3" t="n">
-        <v>141091</v>
+      <c r="A125" s="3" t="s">
+        <v>124</v>
       </c>
       <c r="B125" s="0" t="n">
         <v>2240</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="3" t="n">
-        <v>930295</v>
+      <c r="A126" s="3" t="s">
+        <v>125</v>
       </c>
       <c r="B126" s="0" t="n">
         <v>2760</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="3" t="n">
-        <v>142899</v>
+      <c r="A127" s="3" t="s">
+        <v>126</v>
       </c>
       <c r="B127" s="0" t="n">
         <v>2760</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="3" t="n">
-        <v>142901</v>
+      <c r="A128" s="3" t="s">
+        <v>127</v>
       </c>
       <c r="B128" s="0" t="n">
         <v>2760</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="3" t="n">
-        <v>130298</v>
+      <c r="A129" s="3" t="s">
+        <v>128</v>
       </c>
       <c r="B129" s="0" t="n">
         <v>2760</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="3" t="n">
-        <v>931146</v>
+      <c r="A130" s="3" t="s">
+        <v>129</v>
       </c>
       <c r="B130" s="0" t="n">
         <v>2760</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="3" t="n">
-        <v>138341</v>
+      <c r="A131" s="3" t="s">
+        <v>130</v>
       </c>
       <c r="B131" s="0" t="n">
         <v>1360</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="3" t="n">
-        <v>143123</v>
+      <c r="A132" s="3" t="s">
+        <v>131</v>
       </c>
       <c r="B132" s="0" t="n">
         <v>480</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="3" t="n">
-        <v>942749</v>
+      <c r="A133" s="3" t="s">
+        <v>132</v>
       </c>
       <c r="B133" s="0" t="n">
         <v>590</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="3" t="n">
-        <v>943501</v>
+      <c r="A134" s="3" t="s">
+        <v>133</v>
       </c>
       <c r="B134" s="0" t="n">
         <v>2720</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="3" t="n">
-        <v>135229</v>
+      <c r="A135" s="3" t="s">
+        <v>134</v>
       </c>
       <c r="B135" s="0" t="n">
         <v>2160</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="3" t="n">
-        <v>942181</v>
+      <c r="A136" s="3" t="s">
+        <v>135</v>
       </c>
       <c r="B136" s="0" t="n">
         <v>700</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="3" t="n">
-        <v>138705</v>
+      <c r="A137" s="3" t="s">
+        <v>136</v>
       </c>
       <c r="B137" s="0" t="n">
         <v>910</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="3" t="n">
-        <v>138238</v>
+      <c r="A138" s="3" t="s">
+        <v>137</v>
       </c>
       <c r="B138" s="0" t="n">
         <v>2720</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="3" t="n">
-        <v>914859</v>
+      <c r="A139" s="3" t="s">
+        <v>138</v>
       </c>
       <c r="B139" s="0" t="n">
         <v>910</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="3" t="n">
-        <v>934814</v>
+      <c r="A140" s="3" t="s">
+        <v>139</v>
       </c>
       <c r="B140" s="0" t="n">
         <v>1230</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="3" t="n">
-        <v>938215</v>
+      <c r="A141" s="3" t="s">
+        <v>140</v>
       </c>
       <c r="B141" s="0" t="n">
         <v>2720</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="3" t="n">
-        <v>982371</v>
+      <c r="A142" s="3" t="s">
+        <v>141</v>
       </c>
       <c r="B142" s="0" t="n">
         <v>910</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="3" t="n">
-        <v>115116</v>
+      <c r="A143" s="3" t="s">
+        <v>142</v>
       </c>
       <c r="B143" s="0" t="n">
         <v>2620</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="3" t="n">
-        <v>134305</v>
+      <c r="A144" s="3" t="s">
+        <v>143</v>
       </c>
       <c r="B144" s="0" t="n">
         <v>700</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="3" t="n">
-        <v>138342</v>
+      <c r="A145" s="3" t="s">
+        <v>144</v>
       </c>
       <c r="B145" s="0" t="n">
         <v>1200</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="3" t="n">
-        <v>142852</v>
+      <c r="A146" s="3" t="s">
+        <v>145</v>
       </c>
       <c r="B146" s="0" t="n">
         <v>3260</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="3" t="n">
-        <v>134307</v>
+      <c r="A147" s="3" t="s">
+        <v>146</v>
       </c>
       <c r="B147" s="0" t="n">
         <v>700</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="3" t="n">
-        <v>139067</v>
+      <c r="A148" s="3" t="s">
+        <v>147</v>
       </c>
       <c r="B148" s="0" t="n">
         <v>860</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="3" t="n">
-        <v>942792</v>
+      <c r="A149" s="3" t="s">
+        <v>148</v>
       </c>
       <c r="B149" s="0" t="n">
         <v>1360</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="3" t="n">
-        <v>138773</v>
+      <c r="A150" s="3" t="s">
+        <v>149</v>
       </c>
       <c r="B150" s="0" t="n">
         <v>2890</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="3" t="n">
-        <v>142875</v>
+      <c r="A151" s="3" t="s">
+        <v>150</v>
       </c>
       <c r="B151" s="0" t="n">
         <v>2890</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="3" t="n">
-        <v>127184</v>
+      <c r="A152" s="3" t="s">
+        <v>151</v>
       </c>
       <c r="B152" s="0" t="n">
         <v>2890</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="3" t="n">
-        <v>138791</v>
+      <c r="A153" s="3" t="s">
+        <v>152</v>
       </c>
       <c r="B153" s="0" t="n">
         <v>2890</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="3" t="n">
-        <v>142905</v>
+      <c r="A154" s="3" t="s">
+        <v>153</v>
       </c>
       <c r="B154" s="0" t="n">
         <v>2890</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="3" t="n">
-        <v>938165</v>
+      <c r="A155" s="3" t="s">
+        <v>154</v>
       </c>
       <c r="B155" s="0" t="n">
         <v>910</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="3" t="n">
-        <v>143490</v>
+      <c r="A156" s="3" t="s">
+        <v>155</v>
       </c>
       <c r="B156" s="0" t="n">
         <v>2830</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="3" t="n">
-        <v>139062</v>
+      <c r="A157" s="3" t="s">
+        <v>156</v>
       </c>
       <c r="B157" s="0" t="n">
         <v>660</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="3" t="n">
-        <v>138513</v>
+      <c r="A158" s="3" t="s">
+        <v>157</v>
       </c>
       <c r="B158" s="0" t="n">
         <v>2830</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="3" t="n">
-        <v>142909</v>
+      <c r="A159" s="3" t="s">
+        <v>158</v>
       </c>
       <c r="B159" s="0" t="n">
         <v>2830</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="3" t="n">
-        <v>135246</v>
+      <c r="A160" s="3" t="s">
+        <v>159</v>
       </c>
       <c r="B160" s="0" t="n">
         <v>760</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="3" t="n">
-        <v>923009</v>
+      <c r="A161" s="3" t="s">
+        <v>160</v>
       </c>
       <c r="B161" s="0" t="n">
         <v>1090</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="3" t="n">
-        <v>938170</v>
+      <c r="A162" s="3" t="s">
+        <v>161</v>
       </c>
       <c r="B162" s="0" t="n">
         <v>1090</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="3" t="n">
-        <v>142910</v>
+      <c r="A163" s="3" t="s">
+        <v>162</v>
       </c>
       <c r="B163" s="0" t="n">
         <v>2830</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="3" t="n">
-        <v>142911</v>
+      <c r="A164" s="3" t="s">
+        <v>163</v>
       </c>
       <c r="B164" s="0" t="n">
         <v>2720</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="3" t="n">
-        <v>138794</v>
+      <c r="A165" s="3" t="s">
+        <v>164</v>
       </c>
       <c r="B165" s="0" t="n">
         <v>2830</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="3" t="n">
-        <v>143511</v>
+      <c r="A166" s="3" t="s">
+        <v>165</v>
       </c>
       <c r="B166" s="0" t="n">
         <v>2160</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="3" t="n">
-        <v>938707</v>
+      <c r="A167" s="3" t="s">
+        <v>166</v>
       </c>
       <c r="B167" s="0" t="n">
         <v>1090</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="3" t="n">
-        <v>134851</v>
+      <c r="A168" s="3" t="s">
+        <v>167</v>
       </c>
       <c r="B168" s="0" t="n">
         <v>2350</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="3" t="n">
-        <v>138204</v>
+      <c r="A169" s="3" t="s">
+        <v>168</v>
       </c>
       <c r="B169" s="0" t="n">
         <v>2240</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="3" t="n">
-        <v>130282</v>
+      <c r="A170" s="3" t="s">
+        <v>169</v>
       </c>
       <c r="B170" s="0" t="n">
         <v>2350</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="3" t="n">
-        <v>134220</v>
+      <c r="A171" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="B171" s="0" t="n">
         <v>2160</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="3" t="n">
-        <v>142215</v>
+      <c r="A172" s="3" t="s">
+        <v>171</v>
       </c>
       <c r="B172" s="0" t="n">
         <v>480</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="3" t="n">
-        <v>934815</v>
+      <c r="A173" s="3" t="s">
+        <v>172</v>
       </c>
       <c r="B173" s="0" t="n">
         <v>1200</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="3" t="n">
-        <v>138222</v>
+      <c r="A174" s="3" t="s">
+        <v>173</v>
       </c>
       <c r="B174" s="0" t="n">
         <v>2760</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="3" t="n">
-        <v>119365</v>
+      <c r="A175" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="B175" s="0" t="n">
         <v>2510</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="3" t="n">
-        <v>134816</v>
+      <c r="A176" s="3" t="s">
+        <v>175</v>
       </c>
       <c r="B176" s="0" t="n">
         <v>660</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="3" t="n">
-        <v>938211</v>
+      <c r="A177" s="3" t="s">
+        <v>176</v>
       </c>
       <c r="B177" s="0" t="n">
         <v>2550</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="3" t="n">
-        <v>142216</v>
+      <c r="A178" s="3" t="s">
+        <v>177</v>
       </c>
       <c r="B178" s="0" t="n">
         <v>480</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="3" t="n">
-        <v>935197</v>
+      <c r="A179" s="3" t="s">
+        <v>178</v>
       </c>
       <c r="B179" s="0" t="n">
         <v>730</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="3" t="n">
-        <v>919229</v>
+      <c r="A180" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="B180" s="0" t="n">
         <v>1410</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="3" t="n">
-        <v>134849</v>
+      <c r="A181" s="3" t="s">
+        <v>180</v>
       </c>
       <c r="B181" s="0" t="n">
         <v>2720</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="3" t="n">
-        <v>138208</v>
+      <c r="A182" s="3" t="s">
+        <v>181</v>
       </c>
       <c r="B182" s="0" t="n">
         <v>2300</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="3" t="n">
-        <v>134857</v>
+      <c r="A183" s="3" t="s">
+        <v>182</v>
       </c>
       <c r="B183" s="0" t="n">
         <v>2300</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="3" t="n">
-        <v>142189</v>
+      <c r="A184" s="3" t="s">
+        <v>183</v>
       </c>
       <c r="B184" s="0" t="n">
         <v>2300</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="3" t="n">
-        <v>134859</v>
+      <c r="A185" s="3" t="s">
+        <v>184</v>
       </c>
       <c r="B185" s="0" t="n">
         <v>2300</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="3" t="n">
-        <v>142848</v>
+      <c r="A186" s="3" t="s">
+        <v>185</v>
       </c>
       <c r="B186" s="0" t="n">
         <v>2300</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="3" t="n">
-        <v>138528</v>
+      <c r="A187" s="3" t="s">
+        <v>186</v>
       </c>
       <c r="B187" s="0" t="n">
         <v>2160</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="3" t="n">
-        <v>130281</v>
+      <c r="A188" s="3" t="s">
+        <v>187</v>
       </c>
       <c r="B188" s="0" t="n">
         <v>2240</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="3" t="n">
-        <v>134217</v>
+      <c r="A189" s="3" t="s">
+        <v>188</v>
       </c>
       <c r="B189" s="0" t="n">
         <v>1880</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="3" t="n">
-        <v>142838</v>
+      <c r="A190" s="3" t="s">
+        <v>189</v>
       </c>
       <c r="B190" s="0" t="n">
         <v>2240</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="3" t="n">
-        <v>103159</v>
+      <c r="A191" s="3" t="s">
+        <v>190</v>
       </c>
       <c r="B191" s="0" t="n">
         <v>2070</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="3" t="n">
-        <v>96916</v>
+      <c r="A192" s="3" t="s">
+        <v>191</v>
       </c>
       <c r="B192" s="0" t="n">
         <v>2070</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="3" t="n">
-        <v>107937</v>
+      <c r="A193" s="3" t="s">
+        <v>192</v>
       </c>
       <c r="B193" s="0" t="n">
         <v>910</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="3" t="n">
-        <v>103539</v>
+      <c r="A194" s="3" t="s">
+        <v>193</v>
       </c>
       <c r="B194" s="0" t="n">
         <v>910</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="3" t="n">
-        <v>142190</v>
+      <c r="A195" s="3" t="s">
+        <v>194</v>
       </c>
       <c r="B195" s="0" t="n">
         <v>2070</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="3" t="n">
-        <v>138509</v>
+      <c r="A196" s="3" t="s">
+        <v>195</v>
       </c>
       <c r="B196" s="0" t="n">
         <v>2070</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="3" t="n">
-        <v>143110</v>
+      <c r="A197" s="3" t="s">
+        <v>196</v>
       </c>
       <c r="B197" s="0" t="n">
         <v>2030</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="3" t="n">
-        <v>942183</v>
+      <c r="A198" s="3" t="s">
+        <v>197</v>
       </c>
       <c r="B198" s="0" t="n">
         <v>1090</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="3" t="n">
-        <v>138510</v>
+      <c r="A199" s="3" t="s">
+        <v>198</v>
       </c>
       <c r="B199" s="0" t="n">
         <v>2070</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="3" t="n">
-        <v>938760</v>
+      <c r="A200" s="3" t="s">
+        <v>199</v>
       </c>
       <c r="B200" s="0" t="n">
         <v>1880</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="3" t="n">
-        <v>942761</v>
+      <c r="A201" s="3" t="s">
+        <v>200</v>
       </c>
       <c r="B201" s="0" t="n">
         <v>660</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="3" t="n">
-        <v>142187</v>
+      <c r="A202" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="B202" s="0" t="n">
         <v>2030</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="3" t="n">
-        <v>142836</v>
+      <c r="A203" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="B203" s="0" t="n">
         <v>2030</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="3" t="n">
-        <v>138200</v>
+      <c r="A204" s="3" t="s">
+        <v>203</v>
       </c>
       <c r="B204" s="0" t="n">
         <v>2030</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="3" t="n">
-        <v>138201</v>
+      <c r="A205" s="3" t="s">
+        <v>204</v>
       </c>
       <c r="B205" s="0" t="n">
         <v>2030</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="3" t="n">
-        <v>141093</v>
+      <c r="A206" s="3" t="s">
+        <v>205</v>
       </c>
       <c r="B206" s="0" t="n">
         <v>2160</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="3" t="n">
-        <v>943407</v>
+      <c r="A207" s="3" t="s">
+        <v>206</v>
       </c>
       <c r="B207" s="0" t="n">
         <v>2030</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="3" t="n">
-        <v>139937</v>
+      <c r="A208" s="3" t="s">
+        <v>207</v>
       </c>
       <c r="B208" s="0" t="n">
         <v>2030</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="3" t="n">
-        <v>142859</v>
+      <c r="A209" s="3" t="s">
+        <v>208</v>
       </c>
       <c r="B209" s="0" t="n">
         <v>2030</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="3" t="n">
-        <v>130293</v>
+      <c r="A210" s="3" t="s">
+        <v>209</v>
       </c>
       <c r="B210" s="0" t="n">
         <v>2030</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="3" t="n">
-        <v>927179</v>
+      <c r="A211" s="3" t="s">
+        <v>210</v>
       </c>
       <c r="B211" s="0" t="n">
         <v>2030</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="3" t="n">
-        <v>143512</v>
+      <c r="A212" s="3" t="s">
+        <v>211</v>
       </c>
       <c r="B212" s="0" t="n">
         <v>1480</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="3" t="n">
-        <v>139069</v>
+      <c r="A213" s="3" t="s">
+        <v>212</v>
       </c>
       <c r="B213" s="0" t="n">
         <v>860</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="3" t="n">
-        <v>939154</v>
+      <c r="A214" s="3" t="s">
+        <v>213</v>
       </c>
       <c r="B214" s="0" t="n">
         <v>2030</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="3" t="n">
-        <v>138770</v>
+      <c r="A215" s="3" t="s">
+        <v>214</v>
       </c>
       <c r="B215" s="0" t="n">
         <v>2030</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="3" t="n">
-        <v>130394</v>
+      <c r="A216" s="3" t="s">
+        <v>215</v>
       </c>
       <c r="B216" s="0" t="n">
         <v>2160</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="3" t="n">
-        <v>142758</v>
+      <c r="A217" s="3" t="s">
+        <v>216</v>
       </c>
       <c r="B217" s="0" t="n">
         <v>1090</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="3" t="n">
-        <v>922994</v>
+      <c r="A218" s="3" t="s">
+        <v>217</v>
       </c>
       <c r="B218" s="0" t="n">
         <v>1090</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A219" s="3" t="n">
-        <v>142873</v>
+      <c r="A219" s="3" t="s">
+        <v>218</v>
       </c>
       <c r="B219" s="0" t="n">
         <v>1940</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A220" s="3" t="n">
-        <v>942751</v>
+      <c r="A220" s="3" t="s">
+        <v>219</v>
       </c>
       <c r="B220" s="0" t="n">
         <v>590</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="3" t="n">
-        <v>934822</v>
+      <c r="A221" s="3" t="s">
+        <v>220</v>
       </c>
       <c r="B221" s="0" t="n">
         <v>1380</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A222" s="3" t="n">
-        <v>138843</v>
+      <c r="A222" s="3" t="s">
+        <v>221</v>
       </c>
       <c r="B222" s="0" t="n">
         <v>3090</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A223" s="3" t="n">
-        <v>938161</v>
+      <c r="A223" s="3" t="s">
+        <v>222</v>
       </c>
       <c r="B223" s="0" t="n">
         <v>1480</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A224" s="3" t="n">
-        <v>142186</v>
+      <c r="A224" s="3" t="s">
+        <v>223</v>
       </c>
       <c r="B224" s="0" t="n">
         <v>3960</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A225" s="3" t="n">
-        <v>130338</v>
+      <c r="A225" s="3" t="s">
+        <v>224</v>
       </c>
       <c r="B225" s="0" t="n">
         <v>3020</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A226" s="3" t="n">
-        <v>139966</v>
+      <c r="A226" s="3" t="s">
+        <v>225</v>
       </c>
       <c r="B226" s="0" t="n">
         <v>2890</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A227" s="3" t="n">
-        <v>134283</v>
+      <c r="A227" s="3" t="s">
+        <v>226</v>
       </c>
       <c r="B227" s="0" t="n">
         <v>2620</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A228" s="3" t="n">
-        <v>134957</v>
+      <c r="A228" s="3" t="s">
+        <v>227</v>
       </c>
       <c r="B228" s="0" t="n">
         <v>2480</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A229" s="3" t="n">
-        <v>142964</v>
+      <c r="A229" s="3" t="s">
+        <v>228</v>
       </c>
       <c r="B229" s="0" t="n">
         <v>2350</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A230" s="3" t="n">
-        <v>142206</v>
+      <c r="A230" s="3" t="s">
+        <v>229</v>
       </c>
       <c r="B230" s="0" t="n">
         <v>2350</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A231" s="3" t="n">
-        <v>142965</v>
+      <c r="A231" s="3" t="s">
+        <v>230</v>
       </c>
       <c r="B231" s="0" t="n">
         <v>2350</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A232" s="3" t="n">
-        <v>960565</v>
+      <c r="A232" s="3" t="s">
+        <v>231</v>
       </c>
       <c r="B232" s="0" t="n">
         <v>590</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A233" s="3" t="n">
-        <v>143068</v>
+      <c r="A233" s="3" t="s">
+        <v>232</v>
       </c>
       <c r="B233" s="0" t="n">
         <v>2890</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A234" s="3" t="n">
-        <v>143069</v>
+      <c r="A234" s="3" t="s">
+        <v>233</v>
       </c>
       <c r="B234" s="0" t="n">
         <v>2890</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A235" s="3" t="n">
-        <v>139962</v>
+      <c r="A235" s="3" t="s">
+        <v>234</v>
       </c>
       <c r="B235" s="0" t="n">
         <v>2890</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A236" s="3" t="n">
-        <v>138288</v>
+      <c r="A236" s="3" t="s">
+        <v>235</v>
       </c>
       <c r="B236" s="0" t="n">
         <v>2240</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="3" t="n">
-        <v>138289</v>
+      <c r="A237" s="3" t="s">
+        <v>236</v>
       </c>
       <c r="B237" s="0" t="n">
         <v>2240</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A238" s="3" t="n">
-        <v>138291</v>
+      <c r="A238" s="3" t="s">
+        <v>237</v>
       </c>
       <c r="B238" s="0" t="n">
         <v>2240</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A239" s="3" t="n">
-        <v>142962</v>
+      <c r="A239" s="3" t="s">
+        <v>238</v>
       </c>
       <c r="B239" s="0" t="n">
         <v>2240</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A240" s="3" t="n">
-        <v>138344</v>
+      <c r="A240" s="3" t="s">
+        <v>239</v>
       </c>
       <c r="B240" s="0" t="n">
         <v>1480</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A241" s="3" t="n">
-        <v>942753</v>
+      <c r="A241" s="3" t="s">
+        <v>240</v>
       </c>
       <c r="B241" s="0" t="n">
         <v>590</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A242" s="3" t="n">
-        <v>143497</v>
+      <c r="A242" s="3" t="s">
+        <v>241</v>
       </c>
       <c r="B242" s="0" t="n">
         <v>2830</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A243" s="3" t="n">
-        <v>135020</v>
+      <c r="A243" s="3" t="s">
+        <v>242</v>
       </c>
       <c r="B243" s="0" t="n">
         <v>660</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A244" s="3" t="n">
-        <v>943476</v>
+      <c r="A244" s="3" t="s">
+        <v>243</v>
       </c>
       <c r="B244" s="0" t="n">
         <v>1200</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A245" s="3" t="n">
-        <v>143059</v>
+      <c r="A245" s="3" t="s">
+        <v>244</v>
       </c>
       <c r="B245" s="0" t="n">
         <v>2890</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A246" s="3" t="n">
-        <v>107017</v>
+      <c r="A246" s="3" t="s">
+        <v>245</v>
       </c>
       <c r="B246" s="0" t="n">
         <v>660</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A247" s="3" t="n">
-        <v>960564</v>
+      <c r="A247" s="3" t="s">
+        <v>246</v>
       </c>
       <c r="B247" s="0" t="n">
         <v>590</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A248" s="3" t="n">
-        <v>143060</v>
+      <c r="A248" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="B248" s="0" t="n">
         <v>2760</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A249" s="3" t="n">
-        <v>139063</v>
+      <c r="A249" s="3" t="s">
+        <v>248</v>
       </c>
       <c r="B249" s="0" t="n">
         <v>660</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A250" s="3" t="n">
-        <v>935194</v>
+      <c r="A250" s="3" t="s">
+        <v>249</v>
       </c>
       <c r="B250" s="0" t="n">
         <v>590</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A251" s="3" t="n">
-        <v>938166</v>
+      <c r="A251" s="3" t="s">
+        <v>250</v>
       </c>
       <c r="B251" s="0" t="n">
         <v>590</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A252" s="3" t="n">
-        <v>123314</v>
+      <c r="A252" s="3" t="s">
+        <v>251</v>
       </c>
       <c r="B252" s="0" t="n">
         <v>2450</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A253" s="3" t="n">
-        <v>934809</v>
+      <c r="A253" s="3" t="s">
+        <v>252</v>
       </c>
       <c r="B253" s="0" t="n">
         <v>660</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A254" s="3" t="n">
-        <v>138514</v>
+      <c r="A254" s="3" t="s">
+        <v>253</v>
       </c>
       <c r="B254" s="0" t="n">
         <v>2180</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A255" s="3" t="n">
-        <v>143102</v>
+      <c r="A255" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="B255" s="0" t="n">
         <v>760</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A256" s="3" t="n">
-        <v>907863</v>
+      <c r="A256" s="3" t="s">
+        <v>255</v>
       </c>
       <c r="B256" s="0" t="n">
         <v>760</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A257" s="3" t="n">
-        <v>103187</v>
+      <c r="A257" s="3" t="s">
+        <v>256</v>
       </c>
       <c r="B257" s="0" t="n">
         <v>2160</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A258" s="3" t="n">
-        <v>139941</v>
+      <c r="A258" s="3" t="s">
+        <v>257</v>
       </c>
       <c r="B258" s="0" t="n">
         <v>2160</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A259" s="3" t="n">
-        <v>103528</v>
+      <c r="A259" s="3" t="s">
+        <v>258</v>
       </c>
       <c r="B259" s="0" t="n">
         <v>2160</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A260" s="3" t="n">
-        <v>114978</v>
+      <c r="A260" s="3" t="s">
+        <v>259</v>
       </c>
       <c r="B260" s="0" t="n">
         <v>1940</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A261" s="3" t="n">
-        <v>910793</v>
+      <c r="A261" s="3" t="s">
+        <v>260</v>
       </c>
       <c r="B261" s="0" t="n">
         <v>2160</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A262" s="3" t="n">
-        <v>127069</v>
+      <c r="A262" s="3" t="s">
+        <v>261</v>
       </c>
       <c r="B262" s="0" t="n">
         <v>1230</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A263" s="3" t="n">
-        <v>143019</v>
+      <c r="A263" s="3" t="s">
+        <v>262</v>
       </c>
       <c r="B263" s="0" t="n">
         <v>1830</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A264" s="3" t="n">
-        <v>143122</v>
+      <c r="A264" s="3" t="s">
+        <v>263</v>
       </c>
       <c r="B264" s="0" t="n">
         <v>2030</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A265" s="3" t="n">
-        <v>960562</v>
+      <c r="A265" s="3" t="s">
+        <v>264</v>
       </c>
       <c r="B265" s="0" t="n">
         <v>760</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A266" s="3" t="n">
-        <v>938295</v>
+      <c r="A266" s="3" t="s">
+        <v>265</v>
       </c>
       <c r="B266" s="0" t="n">
         <v>1690</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A267" s="3" t="n">
-        <v>942967</v>
+      <c r="A267" s="3" t="s">
+        <v>266</v>
       </c>
       <c r="B267" s="0" t="n">
         <v>1690</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A268" s="3" t="n">
-        <v>942756</v>
+      <c r="A268" s="3" t="s">
+        <v>267</v>
       </c>
       <c r="B268" s="0" t="n">
         <v>760</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A269" s="3" t="n">
-        <v>938856</v>
+      <c r="A269" s="3" t="s">
+        <v>268</v>
       </c>
       <c r="B269" s="0" t="n">
         <v>1690</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A270" s="3" t="n">
-        <v>138294</v>
+      <c r="A270" s="3" t="s">
+        <v>269</v>
       </c>
       <c r="B270" s="0" t="n">
         <v>1690</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A271" s="3" t="n">
-        <v>938242</v>
+      <c r="A271" s="3" t="s">
+        <v>270</v>
       </c>
       <c r="B271" s="0" t="n">
         <v>2830</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A272" s="3" t="n">
-        <v>931190</v>
+      <c r="A272" s="3" t="s">
+        <v>271</v>
       </c>
       <c r="B272" s="0" t="n">
         <v>2830</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A273" s="3" t="n">
-        <v>134249</v>
+      <c r="A273" s="3" t="s">
+        <v>272</v>
       </c>
       <c r="B273" s="0" t="n">
         <v>2160</v>
       </c>
     </row>
     <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A274" s="3" t="n">
-        <v>942797</v>
+      <c r="A274" s="3" t="s">
+        <v>273</v>
       </c>
       <c r="B274" s="0" t="n">
         <v>1200</v>
       </c>
     </row>
     <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A275" s="3" t="n">
-        <v>143057</v>
+      <c r="A275" s="3" t="s">
+        <v>274</v>
       </c>
       <c r="B275" s="0" t="n">
         <v>2510</v>
       </c>
     </row>
     <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A276" s="3" t="n">
-        <v>143058</v>
+      <c r="A276" s="3" t="s">
+        <v>275</v>
       </c>
       <c r="B276" s="0" t="n">
         <v>2510</v>
       </c>
     </row>
     <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A277" s="3" t="n">
-        <v>938507</v>
+      <c r="A277" s="3" t="s">
+        <v>276</v>
       </c>
       <c r="B277" s="0" t="n">
         <v>910</v>
       </c>
     </row>
     <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A278" s="3" t="n">
-        <v>919342</v>
+      <c r="A278" s="3" t="s">
+        <v>277</v>
       </c>
       <c r="B278" s="0" t="n">
         <v>2300</v>
       </c>
     </row>
     <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A279" s="3" t="n">
-        <v>138255</v>
+      <c r="A279" s="3" t="s">
+        <v>278</v>
       </c>
       <c r="B279" s="0" t="n">
         <v>2300</v>
       </c>
     </row>
     <row r="280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A280" s="3" t="n">
-        <v>139031</v>
+      <c r="A280" s="3" t="s">
+        <v>279</v>
       </c>
       <c r="B280" s="0" t="n">
         <v>2300</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A281" s="3" t="n">
-        <v>139032</v>
+      <c r="A281" s="3" t="s">
+        <v>280</v>
       </c>
       <c r="B281" s="0" t="n">
         <v>2300</v>
       </c>
     </row>
     <row r="282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A282" s="3" t="n">
-        <v>143064</v>
+      <c r="A282" s="3" t="s">
+        <v>281</v>
       </c>
       <c r="B282" s="0" t="n">
         <v>2300</v>
       </c>
     </row>
     <row r="283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A283" s="3" t="n">
-        <v>138297</v>
+      <c r="A283" s="3" t="s">
+        <v>282</v>
       </c>
       <c r="B283" s="0" t="n">
         <v>1940</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A284" s="3" t="n">
-        <v>942970</v>
+      <c r="A284" s="3" t="s">
+        <v>283</v>
       </c>
       <c r="B284" s="0" t="n">
         <v>2300</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A285" s="3" t="n">
-        <v>943063</v>
+      <c r="A285" s="3" t="s">
+        <v>284</v>
       </c>
       <c r="B285" s="0" t="n">
         <v>2300</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A286" s="3" t="n">
-        <v>934958</v>
+      <c r="A286" s="3" t="s">
+        <v>285</v>
       </c>
       <c r="B286" s="0" t="n">
         <v>2300</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A287" s="3" t="n">
-        <v>134284</v>
+      <c r="A287" s="3" t="s">
+        <v>286</v>
       </c>
       <c r="B287" s="0" t="n">
         <v>2300</v>
       </c>
     </row>
     <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A288" s="3" t="n">
-        <v>138857</v>
+      <c r="A288" s="3" t="s">
+        <v>287</v>
       </c>
       <c r="B288" s="0" t="n">
         <v>2300</v>
       </c>
     </row>
     <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A289" s="3" t="n">
-        <v>134811</v>
+      <c r="A289" s="3" t="s">
+        <v>288</v>
       </c>
       <c r="B289" s="0" t="n">
         <v>1090</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A290" s="3" t="n">
-        <v>143020</v>
+      <c r="A290" s="3" t="s">
+        <v>289</v>
       </c>
       <c r="B290" s="0" t="n">
         <v>2350</v>
       </c>
     </row>
     <row r="291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A291" s="3" t="n">
-        <v>143021</v>
+      <c r="A291" s="3" t="s">
+        <v>290</v>
       </c>
       <c r="B291" s="0" t="n">
         <v>2350</v>
       </c>
     </row>
     <row r="292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A292" s="3" t="n">
-        <v>919228</v>
+      <c r="A292" s="3" t="s">
+        <v>291</v>
       </c>
       <c r="B292" s="0" t="n">
         <v>1360</v>
       </c>
     </row>
     <row r="293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A293" s="3" t="n">
-        <v>143054</v>
+      <c r="A293" s="3" t="s">
+        <v>292</v>
       </c>
       <c r="B293" s="0" t="n">
         <v>2760</v>
       </c>
     </row>
     <row r="294" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A294" s="3" t="n">
-        <v>139068</v>
+      <c r="A294" s="3" t="s">
+        <v>293</v>
       </c>
       <c r="B294" s="0" t="n">
         <v>860</v>
       </c>
     </row>
     <row r="295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A295" s="3" t="n">
-        <v>942794</v>
+      <c r="A295" s="3" t="s">
+        <v>294</v>
       </c>
       <c r="B295" s="0" t="n">
         <v>1200</v>
       </c>
     </row>
     <row r="296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A296" s="3" t="n">
-        <v>142203</v>
+      <c r="A296" s="3" t="s">
+        <v>295</v>
       </c>
       <c r="B296" s="0" t="n">
         <v>2350</v>
       </c>
     </row>
     <row r="297" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A297" s="3" t="n">
-        <v>139064</v>
+      <c r="A297" s="3" t="s">
+        <v>296</v>
       </c>
       <c r="B297" s="0" t="n">
         <v>1200</v>
       </c>
     </row>
     <row r="298" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A298" s="3" t="n">
-        <v>143024</v>
+      <c r="A298" s="3" t="s">
+        <v>297</v>
       </c>
       <c r="B298" s="0" t="n">
         <v>2240</v>
       </c>
     </row>
     <row r="299" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A299" s="3" t="n">
-        <v>938329</v>
+      <c r="A299" s="3" t="s">
+        <v>298</v>
       </c>
       <c r="B299" s="0" t="n">
         <v>2240</v>
       </c>
     </row>
     <row r="300" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A300" s="3" t="n">
-        <v>143025</v>
+      <c r="A300" s="3" t="s">
+        <v>299</v>
       </c>
       <c r="B300" s="0" t="n">
         <v>2240</v>
       </c>
     </row>
     <row r="301" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A301" s="3" t="n">
-        <v>942745</v>
+      <c r="A301" s="3" t="s">
+        <v>300</v>
       </c>
       <c r="B301" s="0" t="n">
         <v>760</v>
       </c>
     </row>
     <row r="302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A302" s="3" t="n">
-        <v>942796</v>
+      <c r="A302" s="3" t="s">
+        <v>301</v>
       </c>
       <c r="B302" s="0" t="n">
         <v>1200</v>
       </c>
     </row>
     <row r="303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A303" s="3" t="n">
-        <v>138327</v>
+      <c r="A303" s="3" t="s">
+        <v>302</v>
       </c>
       <c r="B303" s="0" t="n">
         <v>1940</v>
       </c>
     </row>
     <row r="304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A304" s="3" t="n">
-        <v>139033</v>
+      <c r="A304" s="3" t="s">
+        <v>303</v>
       </c>
       <c r="B304" s="0" t="n">
         <v>1940</v>
       </c>
     </row>
     <row r="305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A305" s="3" t="n">
-        <v>931230</v>
+      <c r="A305" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="B305" s="0" t="n">
         <v>2240</v>
       </c>
     </row>
     <row r="306" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A306" s="3" t="n">
-        <v>131231</v>
+      <c r="A306" s="3" t="s">
+        <v>305</v>
       </c>
       <c r="B306" s="0" t="n">
         <v>2240</v>
       </c>
     </row>
     <row r="307" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A307" s="3" t="n">
-        <v>139963</v>
+      <c r="A307" s="3" t="s">
+        <v>306</v>
       </c>
       <c r="B307" s="0" t="n">
         <v>2240</v>
       </c>
     </row>
     <row r="308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A308" s="3" t="n">
-        <v>931232</v>
+      <c r="A308" s="3" t="s">
+        <v>307</v>
       </c>
       <c r="B308" s="0" t="n">
         <v>2240</v>
       </c>
     </row>
     <row r="309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A309" s="3" t="n">
-        <v>131233</v>
+      <c r="A309" s="3" t="s">
+        <v>308</v>
       </c>
       <c r="B309" s="0" t="n">
         <v>2240</v>
       </c>
     </row>
     <row r="310" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A310" s="3" t="n">
-        <v>134306</v>
+      <c r="A310" s="3" t="s">
+        <v>309</v>
       </c>
       <c r="B310" s="0" t="n">
         <v>700</v>
       </c>
     </row>
     <row r="311" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A311" s="3" t="n">
-        <v>143017</v>
+      <c r="A311" s="3" t="s">
+        <v>310</v>
       </c>
       <c r="B311" s="0" t="n">
         <v>2240</v>
       </c>
     </row>
     <row r="312" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A312" s="3" t="n">
-        <v>143018</v>
+      <c r="A312" s="3" t="s">
+        <v>311</v>
       </c>
       <c r="B312" s="0" t="n">
         <v>2240</v>
       </c>
     </row>
     <row r="313" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A313" s="3" t="n">
-        <v>135244</v>
+      <c r="A313" s="3" t="s">
+        <v>312</v>
       </c>
       <c r="B313" s="0" t="n">
         <v>1480</v>
       </c>
     </row>
     <row r="314" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A314" s="3" t="n">
-        <v>934806</v>
+      <c r="A314" s="3" t="s">
+        <v>313</v>
       </c>
       <c r="B314" s="0" t="n">
         <v>1480</v>
       </c>
     </row>
     <row r="315" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A315" s="3" t="n">
-        <v>938838</v>
+      <c r="A315" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="B315" s="0" t="n">
         <v>2160</v>
       </c>
     </row>
     <row r="316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A316" s="3" t="n">
-        <v>938840</v>
+      <c r="A316" s="3" t="s">
+        <v>315</v>
       </c>
       <c r="B316" s="0" t="n">
         <v>2240</v>
       </c>
     </row>
     <row r="317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A317" s="3" t="n">
-        <v>134274</v>
+      <c r="A317" s="3" t="s">
+        <v>316</v>
       </c>
       <c r="B317" s="0" t="n">
         <v>2160</v>
       </c>
     </row>
     <row r="318" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A318" s="3" t="n">
-        <v>134275</v>
+      <c r="A318" s="3" t="s">
+        <v>317</v>
       </c>
       <c r="B318" s="0" t="n">
         <v>2160</v>
       </c>
     </row>
     <row r="319" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A319" s="3" t="n">
-        <v>142951</v>
+      <c r="A319" s="3" t="s">
+        <v>318</v>
       </c>
       <c r="B319" s="0" t="n">
         <v>2160</v>
       </c>
     </row>
     <row r="320" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A320" s="3" t="n">
-        <v>115125</v>
+      <c r="A320" s="3" t="s">
+        <v>319</v>
       </c>
       <c r="B320" s="0" t="n">
         <v>2760</v>
       </c>
     </row>
     <row r="321" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A321" s="3" t="n">
-        <v>130308</v>
+      <c r="A321" s="3" t="s">
+        <v>320</v>
       </c>
       <c r="B321" s="0" t="n">
         <v>2760</v>
       </c>
     </row>
     <row r="322" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A322" s="3" t="n">
-        <v>134893</v>
+      <c r="A322" s="3" t="s">
+        <v>321</v>
       </c>
       <c r="B322" s="0" t="n">
         <v>2760</v>
       </c>
     </row>
     <row r="323" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A323" s="3" t="n">
-        <v>942746</v>
+      <c r="A323" s="3" t="s">
+        <v>322</v>
       </c>
       <c r="B323" s="0" t="n">
         <v>700</v>
       </c>
     </row>
     <row r="324" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A324" s="3" t="n">
-        <v>119429</v>
+      <c r="A324" s="3" t="s">
+        <v>323</v>
       </c>
       <c r="B324" s="0" t="n">
         <v>2760</v>
       </c>
     </row>
     <row r="325" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A325" s="3" t="n">
-        <v>923223</v>
+      <c r="A325" s="3" t="s">
+        <v>324</v>
       </c>
       <c r="B325" s="0" t="n">
         <v>3090</v>
       </c>
     </row>
     <row r="326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A326" s="3" t="n">
-        <v>142766</v>
+      <c r="A326" s="3" t="s">
+        <v>325</v>
       </c>
       <c r="B326" s="0" t="n">
         <v>660</v>
       </c>
     </row>
     <row r="327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A327" s="3" t="n">
-        <v>138318</v>
+      <c r="A327" s="3" t="s">
+        <v>326</v>
       </c>
       <c r="B327" s="0" t="n">
         <v>2620</v>
       </c>
     </row>
     <row r="328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A328" s="3" t="n">
-        <v>143107</v>
+      <c r="A328" s="3" t="s">
+        <v>327</v>
       </c>
       <c r="B328" s="0" t="n">
         <v>1690</v>
       </c>
     </row>
     <row r="329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A329" s="3" t="n">
-        <v>142765</v>
+      <c r="A329" s="3" t="s">
+        <v>328</v>
       </c>
       <c r="B329" s="0" t="n">
         <v>660</v>
       </c>
     </row>
     <row r="330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A330" s="3" t="n">
-        <v>938508</v>
+      <c r="A330" s="3" t="s">
+        <v>329</v>
       </c>
       <c r="B330" s="0" t="n">
         <v>660</v>
       </c>
     </row>
     <row r="331" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A331" s="3" t="n">
-        <v>138319</v>
+      <c r="A331" s="3" t="s">
+        <v>330</v>
       </c>
       <c r="B331" s="0" t="n">
         <v>2620</v>
       </c>
     </row>
     <row r="332" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A332" s="3" t="n">
-        <v>138320</v>
+      <c r="A332" s="3" t="s">
+        <v>331</v>
       </c>
       <c r="B332" s="0" t="n">
         <v>2380</v>
       </c>
     </row>
     <row r="333" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A333" s="3" t="n">
-        <v>942750</v>
+      <c r="A333" s="3" t="s">
+        <v>332</v>
       </c>
       <c r="B333" s="0" t="n">
         <v>590</v>
       </c>
     </row>
     <row r="334" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A334" s="3" t="n">
-        <v>130314</v>
+      <c r="A334" s="3" t="s">
+        <v>333</v>
       </c>
       <c r="B334" s="0" t="n">
         <v>2760</v>
       </c>
     </row>
     <row r="335" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A335" s="3" t="n">
-        <v>139074</v>
+      <c r="A335" s="3" t="s">
+        <v>334</v>
       </c>
       <c r="B335" s="0" t="n">
         <v>760</v>
       </c>
     </row>
     <row r="336" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A336" s="3" t="n">
-        <v>142205</v>
+      <c r="A336" s="3" t="s">
+        <v>335</v>
       </c>
       <c r="B336" s="0" t="n">
         <v>2760</v>
       </c>
     </row>
     <row r="337" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A337" s="3" t="n">
-        <v>139965</v>
+      <c r="A337" s="3" t="s">
+        <v>336</v>
       </c>
       <c r="B337" s="0" t="n">
         <v>2760</v>
       </c>
     </row>
     <row r="338" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A338" s="3" t="n">
-        <v>142961</v>
+      <c r="A338" s="3" t="s">
+        <v>337</v>
       </c>
       <c r="B338" s="0" t="n">
         <v>2760</v>
       </c>
     </row>
     <row r="339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A339" s="3" t="n">
-        <v>126160</v>
+      <c r="A339" s="3" t="s">
+        <v>338</v>
       </c>
       <c r="B339" s="0" t="n">
         <v>2830</v>
       </c>
     </row>
     <row r="340" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A340" s="3" t="n">
-        <v>126161</v>
+      <c r="A340" s="3" t="s">
+        <v>339</v>
       </c>
       <c r="B340" s="0" t="n">
         <v>2830</v>
       </c>
     </row>
     <row r="341" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A341" s="3" t="n">
-        <v>138249</v>
+      <c r="A341" s="3" t="s">
+        <v>340</v>
       </c>
       <c r="B341" s="0" t="n">
         <v>2450</v>
       </c>
     </row>
     <row r="342" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A342" s="3" t="n">
-        <v>942799</v>
+      <c r="A342" s="3" t="s">
+        <v>341</v>
       </c>
       <c r="B342" s="0" t="n">
         <v>1200</v>
       </c>
     </row>
     <row r="343" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A343" s="3" t="n">
-        <v>123306</v>
+      <c r="A343" s="3" t="s">
+        <v>342</v>
       </c>
       <c r="B343" s="0" t="n">
         <v>2620</v>
       </c>
     </row>
     <row r="344" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A344" s="3" t="n">
-        <v>127251</v>
+      <c r="A344" s="3" t="s">
+        <v>343</v>
       </c>
       <c r="B344" s="0" t="n">
         <v>2830</v>
       </c>
     </row>
     <row r="345" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A345" s="3" t="n">
-        <v>123311</v>
+      <c r="A345" s="3" t="s">
+        <v>344</v>
       </c>
       <c r="B345" s="0" t="n">
         <v>1940</v>
       </c>
     </row>
     <row r="346" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A346" s="3" t="n">
-        <v>935009</v>
+      <c r="A346" s="3" t="s">
+        <v>345</v>
       </c>
       <c r="B346" s="0" t="n">
         <v>2510</v>
       </c>
     </row>
     <row r="347" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A347" s="3" t="n">
-        <v>143004</v>
+      <c r="A347" s="3" t="s">
+        <v>346</v>
       </c>
       <c r="B347" s="0" t="n">
         <v>2510</v>
       </c>
     </row>
     <row r="348" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A348" s="3" t="n">
-        <v>138251</v>
+      <c r="A348" s="3" t="s">
+        <v>347</v>
       </c>
       <c r="B348" s="0" t="n">
         <v>1940</v>
       </c>
     </row>
     <row r="349" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A349" s="3" t="n">
-        <v>143108</v>
+      <c r="A349" s="3" t="s">
+        <v>348</v>
       </c>
       <c r="B349" s="0" t="n">
         <v>2030</v>
       </c>
     </row>
     <row r="350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A350" s="3" t="n">
-        <v>123309</v>
+      <c r="A350" s="3" t="s">
+        <v>349</v>
       </c>
       <c r="B350" s="0" t="n">
         <v>2450</v>
       </c>
     </row>
     <row r="351" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A351" s="3" t="n">
-        <v>123310</v>
+      <c r="A351" s="3" t="s">
+        <v>350</v>
       </c>
       <c r="B351" s="0" t="n">
         <v>2450</v>
       </c>
     </row>
     <row r="352" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A352" s="3" t="n">
-        <v>127252</v>
+      <c r="A352" s="3" t="s">
+        <v>351</v>
       </c>
       <c r="B352" s="0" t="n">
         <v>2450</v>
       </c>
     </row>
     <row r="353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A353" s="3" t="n">
-        <v>923295</v>
+      <c r="A353" s="3" t="s">
+        <v>352</v>
       </c>
       <c r="B353" s="0" t="n">
         <v>2450</v>
       </c>
     </row>
     <row r="354" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A354" s="3" t="n">
-        <v>923296</v>
+      <c r="A354" s="3" t="s">
+        <v>353</v>
       </c>
       <c r="B354" s="0" t="n">
         <v>2720</v>
       </c>
     </row>
     <row r="355" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A355" s="3" t="n">
-        <v>123297</v>
+      <c r="A355" s="3" t="s">
+        <v>354</v>
       </c>
       <c r="B355" s="0" t="n">
         <v>2450</v>
       </c>
     </row>
     <row r="356" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A356" s="3" t="n">
-        <v>128169</v>
+      <c r="A356" s="3" t="s">
+        <v>355</v>
       </c>
       <c r="B356" s="0" t="n">
         <v>2830</v>
       </c>
     </row>
     <row r="357" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A357" s="3" t="n">
-        <v>135305</v>
+      <c r="A357" s="3" t="s">
+        <v>356</v>
       </c>
       <c r="B357" s="0" t="n">
         <v>2830</v>
       </c>
     </row>
     <row r="358" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A358" s="3" t="n">
-        <v>135307</v>
+      <c r="A358" s="3" t="s">
+        <v>357</v>
       </c>
       <c r="B358" s="0" t="n">
         <v>2830</v>
       </c>
     </row>
     <row r="359" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A359" s="3" t="n">
-        <v>134904</v>
+      <c r="A359" s="3" t="s">
+        <v>358</v>
       </c>
       <c r="B359" s="0" t="n">
         <v>2450</v>
       </c>
     </row>
     <row r="360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A360" s="3" t="n">
-        <v>138245</v>
+      <c r="A360" s="3" t="s">
+        <v>359</v>
       </c>
       <c r="B360" s="0" t="n">
         <v>1940</v>
       </c>
     </row>
     <row r="361" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A361" s="3" t="n">
-        <v>138246</v>
+      <c r="A361" s="3" t="s">
+        <v>360</v>
       </c>
       <c r="B361" s="0" t="n">
         <v>2240</v>
       </c>
     </row>
     <row r="362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A362" s="3" t="n">
-        <v>138805</v>
+      <c r="A362" s="3" t="s">
+        <v>361</v>
       </c>
       <c r="B362" s="0" t="n">
         <v>1940</v>
       </c>
     </row>
     <row r="363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A363" s="3" t="n">
-        <v>139026</v>
+      <c r="A363" s="3" t="s">
+        <v>362</v>
       </c>
       <c r="B363" s="0" t="n">
         <v>2100</v>
       </c>
     </row>
     <row r="364" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A364" s="3" t="n">
-        <v>135014</v>
+      <c r="A364" s="3" t="s">
+        <v>363</v>
       </c>
       <c r="B364" s="0" t="n">
         <v>760</v>
       </c>
     </row>
     <row r="365" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A365" s="3" t="n">
-        <v>143050</v>
+      <c r="A365" s="3" t="s">
+        <v>364</v>
       </c>
       <c r="B365" s="0" t="n">
         <v>2510</v>
       </c>
     </row>
     <row r="366" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A366" s="3" t="n">
-        <v>143051</v>
+      <c r="A366" s="3" t="s">
+        <v>365</v>
       </c>
       <c r="B366" s="0" t="n">
         <v>2510</v>
       </c>
     </row>
     <row r="367" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A367" s="3" t="n">
-        <v>143052</v>
+      <c r="A367" s="3" t="s">
+        <v>366</v>
       </c>
       <c r="B367" s="0" t="n">
         <v>2620</v>
       </c>
     </row>
     <row r="368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A368" s="3" t="n">
-        <v>928157</v>
+      <c r="A368" s="3" t="s">
+        <v>367</v>
       </c>
       <c r="B368" s="0" t="n">
         <v>910</v>
       </c>
     </row>
     <row r="369" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A369" s="3" t="n">
-        <v>134899</v>
+      <c r="A369" s="3" t="s">
+        <v>368</v>
       </c>
       <c r="B369" s="0" t="n">
         <v>2240</v>
       </c>
     </row>
     <row r="370" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A370" s="3" t="n">
-        <v>134901</v>
+      <c r="A370" s="3" t="s">
+        <v>369</v>
       </c>
       <c r="B370" s="0" t="n">
         <v>2450</v>
       </c>
     </row>
     <row r="371" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A371" s="3" t="n">
-        <v>123288</v>
+      <c r="A371" s="3" t="s">
+        <v>370</v>
       </c>
       <c r="B371" s="0" t="n">
         <v>2450</v>
       </c>
     </row>
     <row r="372" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A372" s="3" t="n">
-        <v>123289</v>
+      <c r="A372" s="3" t="s">
+        <v>371</v>
       </c>
       <c r="B372" s="0" t="n">
         <v>2450</v>
       </c>
     </row>
     <row r="373" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A373" s="3" t="n">
-        <v>135056</v>
+      <c r="A373" s="3" t="s">
+        <v>372</v>
       </c>
       <c r="B373" s="0" t="n">
         <v>2450</v>
       </c>
     </row>
     <row r="374" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A374" s="3" t="n">
-        <v>127244</v>
+      <c r="A374" s="3" t="s">
+        <v>373</v>
       </c>
       <c r="B374" s="0" t="n">
         <v>2450</v>
       </c>
     </row>
     <row r="375" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A375" s="3" t="n">
-        <v>123291</v>
+      <c r="A375" s="3" t="s">
+        <v>374</v>
       </c>
       <c r="B375" s="0" t="n">
         <v>2450</v>
       </c>
     </row>
     <row r="376" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A376" s="3" t="n">
-        <v>138247</v>
+      <c r="A376" s="3" t="s">
+        <v>375</v>
       </c>
       <c r="B376" s="0" t="n">
         <v>2240</v>
       </c>
     </row>
     <row r="377" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A377" s="3" t="n">
-        <v>129039</v>
+      <c r="A377" s="3" t="s">
+        <v>376</v>
       </c>
       <c r="B377" s="0" t="n">
         <v>2720</v>
       </c>
     </row>
     <row r="378" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A378" s="3" t="n">
-        <v>129040</v>
+      <c r="A378" s="3" t="s">
+        <v>377</v>
       </c>
       <c r="B378" s="0" t="n">
         <v>2720</v>
       </c>
     </row>
     <row r="379" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A379" s="3" t="n">
-        <v>142928</v>
+      <c r="A379" s="3" t="s">
+        <v>378</v>
       </c>
       <c r="B379" s="0" t="n">
         <v>2720</v>
       </c>
     </row>
     <row r="380" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A380" s="3" t="n">
-        <v>122957</v>
+      <c r="A380" s="3" t="s">
+        <v>379</v>
       </c>
       <c r="B380" s="0" t="n">
         <v>1480</v>
       </c>
     </row>
     <row r="381" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A381" s="3" t="n">
-        <v>142200</v>
+      <c r="A381" s="3" t="s">
+        <v>380</v>
       </c>
       <c r="B381" s="0" t="n">
         <v>2510</v>
       </c>
     </row>
     <row r="382" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A382" s="3" t="n">
-        <v>134245</v>
+      <c r="A382" s="3" t="s">
+        <v>381</v>
       </c>
       <c r="B382" s="0" t="n">
         <v>2510</v>
       </c>
     </row>
     <row r="383" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A383" s="3" t="n">
-        <v>138273</v>
+      <c r="A383" s="3" t="s">
+        <v>382</v>
       </c>
       <c r="B383" s="0" t="n">
         <v>2510</v>
       </c>
     </row>
     <row r="384" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A384" s="3" t="n">
-        <v>142947</v>
+      <c r="A384" s="3" t="s">
+        <v>383</v>
       </c>
       <c r="B384" s="0" t="n">
         <v>2510</v>
       </c>
     </row>
     <row r="385" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A385" s="3" t="n">
-        <v>142948</v>
+      <c r="A385" s="3" t="s">
+        <v>384</v>
       </c>
       <c r="B385" s="0" t="n">
         <v>2510</v>
       </c>
     </row>
     <row r="386" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A386" s="3" t="n">
-        <v>138519</v>
+      <c r="A386" s="3" t="s">
+        <v>385</v>
       </c>
       <c r="B386" s="0" t="n">
         <v>2510</v>
       </c>
     </row>
     <row r="387" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A387" s="3" t="n">
-        <v>130360</v>
+      <c r="A387" s="3" t="s">
+        <v>386</v>
       </c>
       <c r="B387" s="0" t="n">
         <v>2510</v>
       </c>
     </row>
     <row r="388" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A388" s="3" t="n">
-        <v>142939</v>
+      <c r="A388" s="3" t="s">
+        <v>387</v>
       </c>
       <c r="B388" s="0" t="n">
         <v>2510</v>
       </c>
     </row>
     <row r="389" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A389" s="3" t="n">
-        <v>927066</v>
+      <c r="A389" s="3" t="s">
+        <v>388</v>
       </c>
       <c r="B389" s="0" t="n">
         <v>1230</v>
       </c>
     </row>
     <row r="390" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A390" s="3" t="n">
-        <v>134263</v>
+      <c r="A390" s="3" t="s">
+        <v>389</v>
       </c>
       <c r="B390" s="0" t="n">
         <v>2450</v>
       </c>
     </row>
     <row r="391" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A391" s="3" t="n">
-        <v>143425</v>
+      <c r="A391" s="3" t="s">
+        <v>390</v>
       </c>
       <c r="B391" s="0" t="n">
         <v>2450</v>
       </c>
     </row>
     <row r="392" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A392" s="3" t="n">
-        <v>134264</v>
+      <c r="A392" s="3" t="s">
+        <v>391</v>
       </c>
       <c r="B392" s="0" t="n">
         <v>2450</v>
       </c>
     </row>
     <row r="393" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A393" s="3" t="n">
-        <v>134936</v>
+      <c r="A393" s="3" t="s">
+        <v>392</v>
       </c>
       <c r="B393" s="0" t="n">
         <v>2450</v>
       </c>
     </row>
     <row r="394" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A394" s="3" t="n">
-        <v>142202</v>
+      <c r="A394" s="3" t="s">
+        <v>393</v>
       </c>
       <c r="B394" s="0" t="n">
         <v>2450</v>
       </c>
     </row>
     <row r="395" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A395" s="3" t="n">
-        <v>134262</v>
+      <c r="A395" s="3" t="s">
+        <v>394</v>
       </c>
       <c r="B395" s="0" t="n">
         <v>1830</v>
       </c>
     </row>
     <row r="396" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A396" s="3" t="n">
-        <v>135315</v>
+      <c r="A396" s="3" t="s">
+        <v>395</v>
       </c>
       <c r="B396" s="0" t="n">
         <v>1830</v>
       </c>
     </row>
     <row r="397" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A397" s="3" t="n">
-        <v>143103</v>
+      <c r="A397" s="3" t="s">
+        <v>396</v>
       </c>
       <c r="B397" s="0" t="n">
         <v>1200</v>
       </c>
     </row>
     <row r="398" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A398" s="3" t="n">
-        <v>923318</v>
+      <c r="A398" s="3" t="s">
+        <v>397</v>
       </c>
       <c r="B398" s="0" t="n">
         <v>1940</v>
       </c>
     </row>
     <row r="399" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A399" s="3" t="n">
-        <v>123319</v>
+      <c r="A399" s="3" t="s">
+        <v>398</v>
       </c>
       <c r="B399" s="0" t="n">
         <v>1940</v>
       </c>
     </row>
     <row r="400" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A400" s="3" t="n">
-        <v>139061</v>
+      <c r="A400" s="3" t="s">
+        <v>399</v>
       </c>
       <c r="B400" s="0" t="n">
         <v>500</v>
       </c>
     </row>
     <row r="401" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A401" s="3" t="n">
-        <v>110968</v>
+      <c r="A401" s="3" t="s">
+        <v>400</v>
       </c>
       <c r="B401" s="0" t="n">
         <v>660</v>
       </c>
     </row>
     <row r="402" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A402" s="3" t="n">
-        <v>942752</v>
+      <c r="A402" s="3" t="s">
+        <v>401</v>
       </c>
       <c r="B402" s="0" t="n">
         <v>590</v>
       </c>
     </row>
     <row r="403" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A403" s="3" t="n">
-        <v>142198</v>
+      <c r="A403" s="3" t="s">
+        <v>402</v>
       </c>
       <c r="B403" s="0" t="n">
         <v>2100</v>
       </c>
     </row>
     <row r="404" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A404" s="3" t="n">
-        <v>934236</v>
+      <c r="A404" s="3" t="s">
+        <v>403</v>
       </c>
       <c r="B404" s="0" t="n">
         <v>1940</v>
       </c>
     </row>
     <row r="405" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A405" s="3" t="n">
-        <v>119472</v>
+      <c r="A405" s="3" t="s">
+        <v>404</v>
       </c>
       <c r="B405" s="0" t="n">
         <v>1760</v>
       </c>
     </row>
     <row r="406" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A406" s="3" t="n">
-        <v>930326</v>
+      <c r="A406" s="3" t="s">
+        <v>405</v>
       </c>
       <c r="B406" s="0" t="n">
         <v>2070</v>
       </c>
     </row>
     <row r="407" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A407" s="3" t="n">
-        <v>138800</v>
+      <c r="A407" s="3" t="s">
+        <v>406</v>
       </c>
       <c r="B407" s="0" t="n">
         <v>1760</v>
       </c>
     </row>
     <row r="408" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A408" s="3" t="n">
-        <v>135299</v>
+      <c r="A408" s="3" t="s">
+        <v>407</v>
       </c>
       <c r="B408" s="0" t="n">
         <v>1690</v>
       </c>
     </row>
     <row r="409" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A409" s="3" t="n">
-        <v>123277</v>
+      <c r="A409" s="3" t="s">
+        <v>408</v>
       </c>
       <c r="B409" s="0" t="n">
         <v>1760</v>
       </c>
     </row>
     <row r="410" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A410" s="3" t="n">
-        <v>123278</v>
+      <c r="A410" s="3" t="s">
+        <v>409</v>
       </c>
       <c r="B410" s="0" t="n">
         <v>1760</v>
       </c>
     </row>
     <row r="411" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A411" s="3" t="n">
-        <v>934823</v>
+      <c r="A411" s="3" t="s">
+        <v>410</v>
       </c>
       <c r="B411" s="0" t="n">
         <v>860</v>
       </c>
     </row>
     <row r="412" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A412" s="3" t="n">
-        <v>134279</v>
+      <c r="A412" s="3" t="s">
+        <v>411</v>
       </c>
       <c r="B412" s="0" t="n">
         <v>1940</v>
       </c>
     </row>
     <row r="413" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A413" s="3" t="n">
-        <v>142952</v>
+      <c r="A413" s="3" t="s">
+        <v>412</v>
       </c>
       <c r="B413" s="0" t="n">
         <v>1940</v>
       </c>
     </row>
     <row r="414" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A414" s="3" t="n">
-        <v>128154</v>
+      <c r="A414" s="3" t="s">
+        <v>413</v>
       </c>
       <c r="B414" s="0" t="n">
         <v>910</v>
       </c>
     </row>
     <row r="415" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A415" s="3" t="n">
-        <v>143013</v>
+      <c r="A415" s="3" t="s">
+        <v>414</v>
       </c>
       <c r="B415" s="0" t="n">
         <v>2100</v>
       </c>
     </row>
     <row r="416" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A416" s="3" t="n">
-        <v>143042</v>
+      <c r="A416" s="3" t="s">
+        <v>415</v>
       </c>
       <c r="B416" s="0" t="n">
         <v>2100</v>
       </c>
     </row>
     <row r="417" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A417" s="3" t="n">
-        <v>935201</v>
+      <c r="A417" s="3" t="s">
+        <v>416</v>
       </c>
       <c r="B417" s="0" t="n">
         <v>440</v>
       </c>
     </row>
     <row r="418" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A418" s="3" t="n">
-        <v>938749</v>
+      <c r="A418" s="3" t="s">
+        <v>417</v>
       </c>
       <c r="B418" s="0" t="n">
         <v>1830</v>
       </c>
     </row>
     <row r="419" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A419" s="3" t="n">
-        <v>139065</v>
+      <c r="A419" s="3" t="s">
+        <v>418</v>
       </c>
       <c r="B419" s="0" t="n">
         <v>1480</v>
       </c>
     </row>
     <row r="420" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A420" s="3" t="n">
-        <v>142747</v>
+      <c r="A420" s="3" t="s">
+        <v>419</v>
       </c>
       <c r="B420" s="0" t="n">
         <v>700</v>
       </c>
     </row>
     <row r="421" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A421" s="3" t="n">
-        <v>115182</v>
+      <c r="A421" s="3" t="s">
+        <v>420</v>
       </c>
       <c r="B421" s="0" t="n">
         <v>1900</v>
       </c>
     </row>
     <row r="422" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A422" s="3" t="n">
-        <v>130317</v>
+      <c r="A422" s="3" t="s">
+        <v>421</v>
       </c>
       <c r="B422" s="0" t="n">
         <v>2030</v>
       </c>
     </row>
     <row r="423" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A423" s="3" t="n">
-        <v>922971</v>
+      <c r="A423" s="3" t="s">
+        <v>422</v>
       </c>
       <c r="B423" s="0" t="n">
         <v>1090</v>
       </c>
     </row>
     <row r="424" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A424" s="3" t="n">
-        <v>121127</v>
+      <c r="A424" s="3" t="s">
+        <v>423</v>
       </c>
       <c r="B424" s="0" t="n">
         <v>1900</v>
       </c>
     </row>
     <row r="425" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A425" s="3" t="n">
-        <v>115183</v>
+      <c r="A425" s="3" t="s">
+        <v>424</v>
       </c>
       <c r="B425" s="0" t="n">
         <v>1760</v>
       </c>
     </row>
     <row r="426" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A426" s="3" t="n">
-        <v>134919</v>
+      <c r="A426" s="3" t="s">
+        <v>425</v>
       </c>
       <c r="B426" s="0" t="n">
         <v>1620</v>
       </c>
     </row>
     <row r="427" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A427" s="3" t="n">
-        <v>134920</v>
+      <c r="A427" s="3" t="s">
+        <v>426</v>
       </c>
       <c r="B427" s="0" t="n">
         <v>1620</v>
       </c>
     </row>
     <row r="428" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A428" s="3" t="n">
-        <v>131173</v>
+      <c r="A428" s="3" t="s">
+        <v>427</v>
       </c>
       <c r="B428" s="0" t="n">
         <v>1620</v>
       </c>
     </row>
     <row r="429" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A429" s="3" t="n">
-        <v>134922</v>
+      <c r="A429" s="3" t="s">
+        <v>428</v>
       </c>
       <c r="B429" s="0" t="n">
         <v>1620</v>
       </c>
     </row>
     <row r="430" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A430" s="3" t="n">
-        <v>138256</v>
+      <c r="A430" s="3" t="s">
+        <v>429</v>
       </c>
       <c r="B430" s="0" t="n">
         <v>1620</v>
       </c>
     </row>
     <row r="431" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A431" s="3" t="n">
-        <v>138257</v>
+      <c r="A431" s="3" t="s">
+        <v>430</v>
       </c>
       <c r="B431" s="0" t="n">
         <v>1620</v>
       </c>
     </row>
     <row r="432" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A432" s="3" t="n">
-        <v>134242</v>
+      <c r="A432" s="3" t="s">
+        <v>431</v>
       </c>
       <c r="B432" s="0" t="n">
         <v>1760</v>
       </c>
     </row>
     <row r="433" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A433" s="3" t="n">
-        <v>138308</v>
+      <c r="A433" s="3" t="s">
+        <v>432</v>
       </c>
       <c r="B433" s="0" t="n">
         <v>1760</v>
       </c>
     </row>
     <row r="434" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A434" s="3" t="n">
-        <v>938310</v>
+      <c r="A434" s="3" t="s">
+        <v>433</v>
       </c>
       <c r="B434" s="0" t="n">
         <v>1760</v>
       </c>
     </row>
     <row r="435" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A435" s="3" t="n">
-        <v>934194</v>
+      <c r="A435" s="3" t="s">
+        <v>434</v>
       </c>
       <c r="B435" s="0" t="n">
         <v>760</v>
       </c>
     </row>
     <row r="436" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A436" s="3" t="n">
-        <v>127287</v>
+      <c r="A436" s="3" t="s">
+        <v>435</v>
       </c>
       <c r="B436" s="0" t="n">
         <v>1540</v>
       </c>
     </row>
     <row r="437" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A437" s="3" t="n">
-        <v>927298</v>
+      <c r="A437" s="3" t="s">
+        <v>436</v>
       </c>
       <c r="B437" s="0" t="n">
         <v>1830</v>
       </c>
     </row>
     <row r="438" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A438" s="3" t="n">
-        <v>942182</v>
+      <c r="A438" s="3" t="s">
+        <v>437</v>
       </c>
       <c r="B438" s="0" t="n">
         <v>700</v>
       </c>
     </row>
     <row r="439" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A439" s="3" t="n">
-        <v>127299</v>
+      <c r="A439" s="3" t="s">
+        <v>438</v>
       </c>
       <c r="B439" s="0" t="n">
         <v>1830</v>
       </c>
     </row>
     <row r="440" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A440" s="3" t="n">
-        <v>134260</v>
+      <c r="A440" s="3" t="s">
+        <v>439</v>
       </c>
       <c r="B440" s="0" t="n">
         <v>1580</v>
       </c>
     </row>
     <row r="441" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A441" s="3" t="n">
-        <v>938704</v>
+      <c r="A441" s="3" t="s">
+        <v>440</v>
       </c>
       <c r="B441" s="0" t="n">
         <v>760</v>
       </c>
     </row>
     <row r="442" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A442" s="3" t="n">
-        <v>934272</v>
+      <c r="A442" s="3" t="s">
+        <v>441</v>
       </c>
       <c r="B442" s="0" t="n">
         <v>1830</v>
       </c>
     </row>
     <row r="443" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A443" s="3" t="n">
-        <v>931209</v>
+      <c r="A443" s="3" t="s">
+        <v>442</v>
       </c>
       <c r="B443" s="0" t="n">
         <v>1830</v>
       </c>
     </row>
     <row r="444" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A444" s="3" t="n">
-        <v>928250</v>
+      <c r="A444" s="3" t="s">
+        <v>443</v>
       </c>
       <c r="B444" s="0" t="n">
         <v>1690</v>
       </c>
     </row>
     <row r="445" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A445" s="3" t="n">
-        <v>938829</v>
+      <c r="A445" s="3" t="s">
+        <v>444</v>
       </c>
       <c r="B445" s="0" t="n">
         <v>1380</v>
       </c>
     </row>
     <row r="446" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A446" s="3" t="n">
-        <v>938265</v>
+      <c r="A446" s="3" t="s">
+        <v>445</v>
       </c>
       <c r="B446" s="0" t="n">
         <v>1690</v>
       </c>
     </row>
     <row r="447" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A447" s="3" t="n">
-        <v>927859</v>
+      <c r="A447" s="3" t="s">
+        <v>446</v>
       </c>
       <c r="B447" s="0" t="n">
         <v>1690</v>
       </c>
     </row>
     <row r="448" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A448" s="3" t="n">
-        <v>934253</v>
+      <c r="A448" s="3" t="s">
+        <v>447</v>
       </c>
       <c r="B448" s="0" t="n">
         <v>1690</v>
       </c>
     </row>
     <row r="449" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A449" s="3" t="n">
-        <v>938830</v>
+      <c r="A449" s="3" t="s">
+        <v>448</v>
       </c>
       <c r="B449" s="0" t="n">
         <v>1380</v>
       </c>
     </row>
     <row r="450" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A450" s="3" t="n">
-        <v>931187</v>
+      <c r="A450" s="3" t="s">
+        <v>449</v>
       </c>
       <c r="B450" s="0" t="n">
         <v>1690</v>
       </c>
     </row>
     <row r="451" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A451" s="3" t="n">
-        <v>938827</v>
+      <c r="A451" s="3" t="s">
+        <v>450</v>
       </c>
       <c r="B451" s="0" t="n">
         <v>1690</v>
       </c>
     </row>
     <row r="452" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A452" s="3" t="n">
-        <v>938266</v>
+      <c r="A452" s="3" t="s">
+        <v>451</v>
       </c>
       <c r="B452" s="0" t="n">
         <v>1690</v>
       </c>
     </row>
     <row r="453" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A453" s="3" t="n">
-        <v>938164</v>
+      <c r="A453" s="3" t="s">
+        <v>452</v>
       </c>
       <c r="B453" s="0" t="n">
         <v>910</v>
       </c>
     </row>
     <row r="454" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A454" s="3" t="n">
-        <v>134244</v>
+      <c r="A454" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="B454" s="0" t="n">
         <v>1300</v>
       </c>
     </row>
     <row r="455" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A455" s="3" t="n">
-        <v>938263</v>
+      <c r="A455" s="3" t="s">
+        <v>454</v>
       </c>
       <c r="B455" s="0" t="n">
         <v>1690</v>
       </c>
     </row>
     <row r="456" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A456" s="3" t="n">
-        <v>942180</v>
+      <c r="A456" s="3" t="s">
+        <v>455</v>
       </c>
       <c r="B456" s="0" t="n">
         <v>700</v>
       </c>
     </row>
     <row r="457" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A457" s="3" t="n">
-        <v>934187</v>
+      <c r="A457" s="3" t="s">
+        <v>456</v>
       </c>
       <c r="B457" s="0" t="n">
         <v>910</v>
       </c>
     </row>
     <row r="458" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A458" s="3" t="n">
-        <v>138322</v>
+      <c r="A458" s="3" t="s">
+        <v>457</v>
       </c>
       <c r="B458" s="0" t="n">
         <v>1870</v>
       </c>
     </row>
     <row r="459" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A459" s="3" t="n">
-        <v>123114</v>
+      <c r="A459" s="3" t="s">
+        <v>458</v>
       </c>
       <c r="B459" s="0" t="n">
         <v>1620</v>
       </c>
     </row>
     <row r="460" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A460" s="3" t="n">
-        <v>131137</v>
+      <c r="A460" s="3" t="s">
+        <v>459</v>
       </c>
       <c r="B460" s="0" t="n">
         <v>1620</v>
       </c>
     </row>
     <row r="461" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A461" s="3" t="n">
-        <v>931138</v>
+      <c r="A461" s="3" t="s">
+        <v>460</v>
       </c>
       <c r="B461" s="0" t="n">
         <v>1300</v>
       </c>
     </row>
     <row r="462" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A462" s="3" t="n">
-        <v>103173</v>
+      <c r="A462" s="3" t="s">
+        <v>461</v>
       </c>
       <c r="B462" s="0" t="n">
         <v>1620</v>
       </c>
     </row>
     <row r="463" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A463" s="3" t="n">
-        <v>107911</v>
+      <c r="A463" s="3" t="s">
+        <v>462</v>
       </c>
       <c r="B463" s="0" t="n">
         <v>1620</v>
       </c>
     </row>
     <row r="464" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A464" s="3" t="n">
-        <v>114985</v>
+      <c r="A464" s="3" t="s">
+        <v>463</v>
       </c>
       <c r="B464" s="0" t="n">
         <v>1620</v>
       </c>
     </row>
     <row r="465" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A465" s="3" t="n">
-        <v>927207</v>
+      <c r="A465" s="3" t="s">
+        <v>464</v>
       </c>
       <c r="B465" s="0" t="n">
         <v>910</v>
       </c>
     </row>
     <row r="466" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A466" s="3" t="n">
-        <v>143027</v>
+      <c r="A466" s="3" t="s">
+        <v>465</v>
       </c>
       <c r="B466" s="0" t="n">
         <v>860</v>
       </c>
     </row>
     <row r="467" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A467" s="3" t="n">
-        <v>943028</v>
+      <c r="A467" s="3" t="s">
+        <v>466</v>
       </c>
       <c r="B467" s="0" t="n">
         <v>860</v>
       </c>
     </row>
     <row r="468" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A468" s="3" t="n">
-        <v>938173</v>
+      <c r="A468" s="3" t="s">
+        <v>467</v>
       </c>
       <c r="B468" s="0" t="n">
         <v>1200</v>
       </c>
     </row>
     <row r="469" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A469" s="3" t="n">
-        <v>142196</v>
+      <c r="A469" s="3" t="s">
+        <v>468</v>
       </c>
       <c r="B469" s="0" t="n">
         <v>1130</v>
       </c>
     </row>
     <row r="470" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A470" s="3" t="n">
-        <v>143414</v>
+      <c r="A470" s="3" t="s">
+        <v>469</v>
       </c>
       <c r="B470" s="0" t="n">
         <v>1130</v>
       </c>
     </row>
     <row r="471" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A471" s="3" t="n">
-        <v>927064</v>
+      <c r="A471" s="3" t="s">
+        <v>470</v>
       </c>
       <c r="B471" s="0" t="n">
         <v>1130</v>
       </c>
     </row>
     <row r="472" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A472" s="3" t="n">
-        <v>902891</v>
+      <c r="A472" s="3" t="s">
+        <v>471</v>
       </c>
       <c r="B472" s="0" t="n">
         <v>1130</v>
       </c>
     </row>
     <row r="473" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A473" s="3" t="n">
-        <v>123112</v>
+      <c r="A473" s="3" t="s">
+        <v>472</v>
       </c>
       <c r="B473" s="0" t="n">
         <v>1130</v>
       </c>
     </row>
     <row r="474" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A474" s="3" t="n">
-        <v>143363</v>
+      <c r="A474" s="3" t="s">
+        <v>473</v>
       </c>
       <c r="B474" s="0" t="n">
         <v>810</v>
       </c>
     </row>
     <row r="475" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A475" s="3" t="n">
-        <v>138553</v>
+      <c r="A475" s="3" t="s">
+        <v>474</v>
       </c>
       <c r="B475" s="0" t="n">
         <v>810</v>
       </c>
     </row>
     <row r="476" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A476" s="3" t="n">
-        <v>135074</v>
+      <c r="A476" s="3" t="s">
+        <v>475</v>
       </c>
       <c r="B476" s="0" t="n">
         <v>810</v>
       </c>
     </row>
     <row r="477" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A477" s="3" t="n">
-        <v>135323</v>
+      <c r="A477" s="3" t="s">
+        <v>476</v>
       </c>
       <c r="B477" s="0" t="n">
         <v>2070</v>
       </c>
     </row>
     <row r="478" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A478" s="3" t="n">
-        <v>114252</v>
+      <c r="A478" s="3" t="s">
+        <v>477</v>
       </c>
       <c r="B478" s="0" t="n">
         <v>2860</v>
       </c>
     </row>
     <row r="479" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A479" s="3" t="n">
-        <v>130808</v>
+      <c r="A479" s="3" t="s">
+        <v>478</v>
       </c>
       <c r="B479" s="0" t="n">
         <v>2860</v>
       </c>
     </row>
     <row r="480" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A480" s="3" t="n">
-        <v>114255</v>
+      <c r="A480" s="3" t="s">
+        <v>479</v>
       </c>
       <c r="B480" s="0" t="n">
         <v>2720</v>
       </c>
     </row>
     <row r="481" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A481" s="3" t="n">
-        <v>114262</v>
+      <c r="A481" s="3" t="s">
+        <v>480</v>
       </c>
       <c r="B481" s="0" t="n">
         <v>2720</v>
       </c>
     </row>
     <row r="482" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A482" s="3" t="n">
-        <v>130813</v>
+      <c r="A482" s="3" t="s">
+        <v>481</v>
       </c>
       <c r="B482" s="0" t="n">
         <v>2410</v>
       </c>
     </row>
     <row r="483" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A483" s="3" t="n">
-        <v>134119</v>
+      <c r="A483" s="3" t="s">
+        <v>482</v>
       </c>
       <c r="B483" s="0" t="n">
         <v>2380</v>
       </c>
     </row>
     <row r="484" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A484" s="3" t="n">
-        <v>143362</v>
+      <c r="A484" s="3" t="s">
+        <v>483</v>
       </c>
       <c r="B484" s="0" t="n">
         <v>1480</v>
       </c>
     </row>
     <row r="485" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A485" s="3" t="n">
-        <v>138551</v>
+      <c r="A485" s="3" t="s">
+        <v>484</v>
       </c>
       <c r="B485" s="0" t="n">
         <v>1480</v>
       </c>
     </row>
     <row r="486" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A486" s="3" t="n">
-        <v>138552</v>
+      <c r="A486" s="3" t="s">
+        <v>485</v>
       </c>
       <c r="B486" s="0" t="n">
         <v>1480</v>
       </c>
     </row>
     <row r="487" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A487" s="3" t="n">
-        <v>134117</v>
+      <c r="A487" s="3" t="s">
+        <v>486</v>
       </c>
       <c r="B487" s="0" t="n">
         <v>2240</v>
       </c>
     </row>
     <row r="488" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A488" s="3" t="n">
-        <v>134118</v>
+      <c r="A488" s="3" t="s">
+        <v>487</v>
       </c>
       <c r="B488" s="0" t="n">
         <v>1900</v>
       </c>
     </row>
     <row r="489" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A489" s="3" t="n">
-        <v>122636</v>
+      <c r="A489" s="3" t="s">
+        <v>488</v>
       </c>
       <c r="B489" s="0" t="n">
         <v>2240</v>
       </c>
     </row>
     <row r="490" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A490" s="3" t="n">
-        <v>119136</v>
+      <c r="A490" s="3" t="s">
+        <v>489</v>
       </c>
       <c r="B490" s="0" t="n">
         <v>2030</v>
       </c>
     </row>
     <row r="491" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A491" s="3" t="n">
-        <v>138463</v>
+      <c r="A491" s="3" t="s">
+        <v>490</v>
       </c>
       <c r="B491" s="0" t="n">
         <v>2240</v>
       </c>
     </row>
     <row r="492" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A492" s="3" t="n">
-        <v>114268</v>
+      <c r="A492" s="3" t="s">
+        <v>491</v>
       </c>
       <c r="B492" s="0" t="n">
         <v>2030</v>
       </c>
     </row>
     <row r="493" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A493" s="3" t="n">
-        <v>122633</v>
+      <c r="A493" s="3" t="s">
+        <v>492</v>
       </c>
       <c r="B493" s="0" t="n">
         <v>2240</v>
       </c>
     </row>
     <row r="494" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A494" s="3" t="n">
-        <v>122634</v>
+      <c r="A494" s="3" t="s">
+        <v>493</v>
       </c>
       <c r="B494" s="0" t="n">
         <v>2240</v>
       </c>
     </row>
     <row r="495" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A495" s="3" t="n">
-        <v>138550</v>
+      <c r="A495" s="3" t="s">
+        <v>494</v>
       </c>
       <c r="B495" s="0" t="n">
         <v>2030</v>
       </c>
     </row>
     <row r="496" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A496" s="3" t="n">
-        <v>138464</v>
+      <c r="A496" s="3" t="s">
+        <v>495</v>
       </c>
       <c r="B496" s="0" t="n">
         <v>2030</v>
       </c>
     </row>
     <row r="497" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A497" s="3" t="n">
-        <v>134121</v>
+      <c r="A497" s="3" t="s">
+        <v>496</v>
       </c>
       <c r="B497" s="0" t="n">
         <v>2180</v>
       </c>
     </row>
     <row r="498" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A498" s="3" t="n">
-        <v>138461</v>
+      <c r="A498" s="3" t="s">
+        <v>497</v>
       </c>
       <c r="B498" s="0" t="n">
         <v>2790</v>
       </c>
     </row>
     <row r="499" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A499" s="3" t="n">
-        <v>138462</v>
+      <c r="A499" s="3" t="s">
+        <v>498</v>
       </c>
       <c r="B499" s="0" t="n">
         <v>2790</v>
       </c>
     </row>
     <row r="500" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A500" s="3" t="n">
-        <v>130816</v>
+      <c r="A500" s="3" t="s">
+        <v>499</v>
       </c>
       <c r="B500" s="0" t="n">
         <v>2240</v>
       </c>
     </row>
     <row r="501" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A501" s="3" t="n">
-        <v>138465</v>
+      <c r="A501" s="3" t="s">
+        <v>500</v>
       </c>
       <c r="B501" s="0" t="n">
         <v>1900</v>
       </c>
     </row>
     <row r="502" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A502" s="3" t="n">
-        <v>138466</v>
+      <c r="A502" s="3" t="s">
+        <v>501</v>
       </c>
       <c r="B502" s="0" t="n">
         <v>1900</v>
       </c>
     </row>
     <row r="503" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A503" s="3" t="n">
-        <v>114272</v>
+      <c r="A503" s="3" t="s">
+        <v>502</v>
       </c>
       <c r="B503" s="0" t="n">
         <v>2330</v>
       </c>
     </row>
     <row r="504" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A504" s="3" t="n">
-        <v>129303</v>
+      <c r="A504" s="3" t="s">
+        <v>503</v>
       </c>
       <c r="B504" s="0" t="n">
         <v>2330</v>
       </c>
     </row>
     <row r="505" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A505" s="3" t="n">
-        <v>141460</v>
+      <c r="A505" s="3" t="s">
+        <v>504</v>
       </c>
       <c r="B505" s="0" t="n">
         <v>2330</v>
       </c>
     </row>
     <row r="506" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A506" s="3" t="n">
-        <v>141462</v>
+      <c r="A506" s="3" t="s">
+        <v>505</v>
       </c>
       <c r="B506" s="0" t="n">
         <v>2480</v>
       </c>
     </row>
     <row r="507" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A507" s="3" t="n">
-        <v>141463</v>
+      <c r="A507" s="3" t="s">
+        <v>506</v>
       </c>
       <c r="B507" s="0" t="n">
         <v>2950</v>
       </c>
     </row>
     <row r="508" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A508" s="3" t="n">
-        <v>141461</v>
+      <c r="A508" s="3" t="s">
+        <v>507</v>
       </c>
       <c r="B508" s="0" t="n">
         <v>1930</v>
       </c>
     </row>
     <row r="509" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A509" s="3" t="n">
-        <v>141458</v>
+      <c r="A509" s="3" t="s">
+        <v>508</v>
       </c>
       <c r="B509" s="0" t="n">
         <v>2480</v>
       </c>
     </row>
     <row r="510" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A510" s="3" t="n">
-        <v>141459</v>
+      <c r="A510" s="3" t="s">
+        <v>509</v>
       </c>
       <c r="B510" s="0" t="n">
         <v>2480</v>
       </c>
     </row>
     <row r="511" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A511" s="3" t="n">
-        <v>943437</v>
+      <c r="A511" s="3" t="s">
+        <v>510</v>
       </c>
       <c r="B511" s="0" t="n">
         <v>480</v>
       </c>
     </row>
     <row r="512" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A512" s="3" t="n">
-        <v>943438</v>
+      <c r="A512" s="3" t="s">
+        <v>511</v>
       </c>
       <c r="B512" s="0" t="n">
         <v>370</v>
       </c>
     </row>
     <row r="513" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A513" s="3" t="n">
-        <v>841739</v>
+      <c r="A513" s="3" t="s">
+        <v>512</v>
       </c>
       <c r="B513" s="0" t="n">
         <v>750</v>
       </c>
     </row>
     <row r="514" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A514" s="3" t="n">
-        <v>143439</v>
+      <c r="A514" s="3" t="s">
+        <v>513</v>
       </c>
       <c r="B514" s="0" t="n">
         <v>590</v>
       </c>
     </row>
     <row r="515" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A515" s="3" t="n">
-        <v>943441</v>
+      <c r="A515" s="3" t="s">
+        <v>514</v>
       </c>
       <c r="B515" s="0" t="n">
         <v>340</v>
       </c>
     </row>
     <row r="516" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A516" s="3" t="n">
-        <v>735688</v>
+      <c r="A516" s="3" t="s">
+        <v>515</v>
       </c>
       <c r="B516" s="0" t="n">
         <v>1300</v>
       </c>
     </row>
     <row r="517" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A517" s="3" t="n">
-        <v>943436</v>
+      <c r="A517" s="3" t="s">
+        <v>516</v>
       </c>
       <c r="B517" s="0" t="n">
         <v>410</v>
       </c>
     </row>
     <row r="518" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A518" s="3" t="n">
-        <v>943440</v>
+      <c r="A518" s="3" t="s">
+        <v>517</v>
       </c>
       <c r="B518" s="0" t="n">
         <v>590</v>
       </c>
     </row>
     <row r="519" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A519" s="3" t="n">
-        <v>942507</v>
+      <c r="A519" s="3" t="s">
+        <v>518</v>
       </c>
       <c r="B519" s="0" t="n">
         <v>650</v>
       </c>
     </row>
     <row r="520" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A520" s="3" t="n">
-        <v>142514</v>
+      <c r="A520" s="3" t="s">
+        <v>519</v>
       </c>
       <c r="B520" s="0" t="n">
         <v>810</v>
       </c>
     </row>
     <row r="521" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A521" s="3" t="n">
-        <v>942516</v>
+      <c r="A521" s="3" t="s">
+        <v>520</v>
       </c>
       <c r="B521" s="0" t="n">
         <v>650</v>
       </c>
     </row>
     <row r="522" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A522" s="3" t="n">
-        <v>127778</v>
+      <c r="A522" s="3" t="s">
+        <v>521</v>
       </c>
       <c r="B522" s="0" t="n">
         <v>1900</v>
       </c>
     </row>
     <row r="523" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A523" s="3" t="n">
-        <v>943369</v>
+      <c r="A523" s="3" t="s">
+        <v>522</v>
       </c>
       <c r="B523" s="0" t="n">
         <v>650</v>
       </c>
     </row>
     <row r="524" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A524" s="3" t="n">
-        <v>942515</v>
+      <c r="A524" s="3" t="s">
+        <v>523</v>
       </c>
       <c r="B524" s="0" t="n">
         <v>970</v>
       </c>
     </row>
     <row r="525" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A525" s="3" t="n">
-        <v>130828</v>
+      <c r="A525" s="3" t="s">
+        <v>524</v>
       </c>
       <c r="B525" s="0" t="n">
         <v>1090</v>
       </c>
     </row>
     <row r="526" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A526" s="3" t="n">
-        <v>942512</v>
+      <c r="A526" s="3" t="s">
+        <v>525</v>
       </c>
       <c r="B526" s="0" t="n">
         <v>620</v>
       </c>
     </row>
     <row r="527" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A527" s="3" t="n">
-        <v>130179</v>
+      <c r="A527" s="3" t="s">
+        <v>526</v>
       </c>
       <c r="B527" s="0" t="n">
         <v>810</v>
       </c>
     </row>
     <row r="528" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A528" s="3" t="n">
-        <v>52998</v>
+      <c r="A528" s="3" t="s">
+        <v>527</v>
       </c>
       <c r="B528" s="0" t="n">
         <v>470</v>
       </c>
     </row>
     <row r="529" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A529" s="3" t="n">
-        <v>134136</v>
+      <c r="A529" s="3" t="s">
+        <v>528</v>
       </c>
       <c r="B529" s="0" t="n">
         <v>1090</v>
       </c>
     </row>
     <row r="530" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A530" s="3" t="n">
-        <v>138482</v>
+      <c r="A530" s="3" t="s">
+        <v>529</v>
       </c>
       <c r="B530" s="0" t="n">
         <v>1370</v>
       </c>
     </row>
     <row r="531" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A531" s="3" t="n">
-        <v>938487</v>
+      <c r="A531" s="3" t="s">
+        <v>530</v>
       </c>
       <c r="B531" s="0" t="n">
         <v>1130</v>
       </c>
     </row>
     <row r="532" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A532" s="3" t="n">
-        <v>142517</v>
+      <c r="A532" s="3" t="s">
+        <v>531</v>
       </c>
       <c r="B532" s="0" t="n">
         <v>520</v>
       </c>
     </row>
     <row r="533" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A533" s="3" t="n">
-        <v>942509</v>
+      <c r="A533" s="3" t="s">
+        <v>532</v>
       </c>
       <c r="B533" s="0" t="n">
         <v>1120</v>
       </c>
     </row>
     <row r="534" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A534" s="3" t="n">
-        <v>142510</v>
+      <c r="A534" s="3" t="s">
+        <v>533</v>
       </c>
       <c r="B534" s="0" t="n">
         <v>1090</v>
       </c>
     </row>
     <row r="535" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A535" s="3" t="n">
-        <v>142513</v>
+      <c r="A535" s="3" t="s">
+        <v>534</v>
       </c>
       <c r="B535" s="0" t="n">
         <v>1480</v>
       </c>
     </row>
     <row r="536" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A536" s="3" t="n">
-        <v>138480</v>
+      <c r="A536" s="3" t="s">
+        <v>535</v>
       </c>
       <c r="B536" s="0" t="n">
         <v>1370</v>
       </c>
     </row>
     <row r="537" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A537" s="3" t="n">
-        <v>138481</v>
+      <c r="A537" s="3" t="s">
+        <v>536</v>
       </c>
       <c r="B537" s="0" t="n">
         <v>1370</v>
       </c>
     </row>
     <row r="538" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A538" s="3" t="n">
-        <v>942518</v>
+      <c r="A538" s="3" t="s">
+        <v>537</v>
       </c>
       <c r="B538" s="0" t="n">
         <v>1090</v>
       </c>
     </row>
     <row r="539" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A539" s="3" t="n">
-        <v>88550</v>
+      <c r="A539" s="3" t="s">
+        <v>538</v>
       </c>
       <c r="B539" s="0" t="n">
         <v>6140</v>
       </c>
     </row>
     <row r="540" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A540" s="3" t="n">
-        <v>134352</v>
+      <c r="A540" s="3" t="s">
+        <v>539</v>
       </c>
       <c r="B540" s="0" t="n">
         <v>6140</v>
       </c>
     </row>
     <row r="541" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A541" s="3" t="n">
-        <v>138559</v>
+      <c r="A541" s="3" t="s">
+        <v>540</v>
       </c>
       <c r="B541" s="0" t="n">
         <v>1630</v>
       </c>
     </row>
     <row r="542" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A542" s="3" t="n">
-        <v>142549</v>
+      <c r="A542" s="3" t="s">
+        <v>541</v>
       </c>
       <c r="B542" s="0" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="543" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A543" s="3" t="n">
-        <v>130807</v>
+      <c r="A543" s="3" t="s">
+        <v>542</v>
       </c>
       <c r="B543" s="0" t="n">
         <v>6000</v>
       </c>
     </row>
     <row r="544" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A544" s="3" t="n">
-        <v>114530</v>
+      <c r="A544" s="3" t="s">
+        <v>543</v>
       </c>
       <c r="B544" s="0" t="n">
         <v>480</v>
       </c>
     </row>
     <row r="545" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A545" s="3" t="n">
-        <v>142551</v>
+      <c r="A545" s="3" t="s">
+        <v>544</v>
       </c>
       <c r="B545" s="0" t="n">
         <v>950</v>
       </c>
     </row>
     <row r="546" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A546" s="3" t="n">
-        <v>142553</v>
+      <c r="A546" s="3" t="s">
+        <v>545</v>
       </c>
       <c r="B546" s="0" t="n">
         <v>480</v>
       </c>
     </row>
     <row r="547" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A547" s="3" t="n">
-        <v>119774</v>
+      <c r="A547" s="3" t="s">
+        <v>546</v>
       </c>
       <c r="B547" s="0" t="n">
         <v>3760</v>
       </c>
     </row>
     <row r="548" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A548" s="3" t="n">
-        <v>143398</v>
+      <c r="A548" s="3" t="s">
+        <v>547</v>
       </c>
       <c r="B548" s="0" t="n">
         <v>330</v>
       </c>
     </row>
     <row r="549" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A549" s="3" t="n">
-        <v>113020</v>
+      <c r="A549" s="3" t="s">
+        <v>548</v>
       </c>
       <c r="B549" s="0" t="n">
         <v>3760</v>
       </c>
     </row>
     <row r="550" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A550" s="3" t="n">
-        <v>106195</v>
+      <c r="A550" s="3" t="s">
+        <v>549</v>
       </c>
       <c r="B550" s="0" t="n">
         <v>3760</v>
       </c>
     </row>
     <row r="551" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A551" s="3" t="n">
-        <v>143395</v>
+      <c r="A551" s="3" t="s">
+        <v>550</v>
       </c>
       <c r="B551" s="0" t="n">
         <v>630</v>
       </c>
     </row>
     <row r="552" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A552" s="3" t="n">
-        <v>130195</v>
+      <c r="A552" s="3" t="s">
+        <v>551</v>
       </c>
       <c r="B552" s="0" t="n">
         <v>810</v>
       </c>
     </row>
     <row r="553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A553" s="3" t="n">
-        <v>130805</v>
+      <c r="A553" s="3" t="s">
+        <v>552</v>
       </c>
       <c r="B553" s="0" t="n">
         <v>4730</v>
       </c>
     </row>
     <row r="554" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A554" s="3" t="n">
-        <v>122808</v>
+      <c r="A554" s="3" t="s">
+        <v>553</v>
       </c>
       <c r="B554" s="0" t="n">
         <v>1880</v>
       </c>
     </row>
     <row r="555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A555" s="3" t="n">
-        <v>110346</v>
+      <c r="A555" s="3" t="s">
+        <v>554</v>
       </c>
       <c r="B555" s="0" t="n">
         <v>4730</v>
       </c>
     </row>
     <row r="556" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A556" s="3" t="n">
-        <v>122824</v>
+      <c r="A556" s="3" t="s">
+        <v>555</v>
       </c>
       <c r="B556" s="0" t="n">
         <v>410</v>
       </c>
     </row>
     <row r="557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A557" s="3" t="n">
-        <v>128143</v>
+      <c r="A557" s="3" t="s">
+        <v>556</v>
       </c>
       <c r="B557" s="0" t="n">
         <v>810</v>
       </c>
     </row>
     <row r="558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A558" s="3" t="n">
-        <v>110441</v>
+      <c r="A558" s="3" t="s">
+        <v>557</v>
       </c>
       <c r="B558" s="0" t="n">
         <v>510</v>
       </c>
     </row>
     <row r="559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A559" s="3" t="n">
-        <v>96357</v>
+      <c r="A559" s="3" t="s">
+        <v>558</v>
       </c>
       <c r="B559" s="0" t="n">
         <v>4960</v>
       </c>
     </row>
     <row r="560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A560" s="3" t="n">
-        <v>143397</v>
+      <c r="A560" s="3" t="s">
+        <v>559</v>
       </c>
       <c r="B560" s="0" t="n">
         <v>370</v>
       </c>
     </row>
     <row r="561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A561" s="3" t="n">
-        <v>119586</v>
+      <c r="A561" s="3" t="s">
+        <v>560</v>
       </c>
       <c r="B561" s="0" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A562" s="3" t="n">
-        <v>940646</v>
+      <c r="A562" s="3" t="s">
+        <v>561</v>
       </c>
       <c r="B562" s="0" t="n">
         <v>3870</v>
       </c>
     </row>
     <row r="563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A563" s="3" t="n">
-        <v>119597</v>
+      <c r="A563" s="3" t="s">
+        <v>562</v>
       </c>
       <c r="B563" s="0" t="n">
         <v>480</v>
       </c>
     </row>
     <row r="564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A564" s="3" t="n">
-        <v>110440</v>
+      <c r="A564" s="3" t="s">
+        <v>563</v>
       </c>
       <c r="B564" s="0" t="n">
         <v>470</v>
       </c>
     </row>
     <row r="565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A565" s="3" t="n">
-        <v>110445</v>
+      <c r="A565" s="3" t="s">
+        <v>564</v>
       </c>
       <c r="B565" s="0" t="n">
         <v>490</v>
       </c>
     </row>
     <row r="566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A566" s="3" t="n">
-        <v>134720</v>
+      <c r="A566" s="3" t="s">
+        <v>565</v>
       </c>
       <c r="B566" s="0" t="n">
         <v>2620</v>
       </c>
     </row>
     <row r="567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A567" s="3" t="n">
-        <v>122789</v>
+      <c r="A567" s="3" t="s">
+        <v>566</v>
       </c>
       <c r="B567" s="0" t="n">
         <v>870</v>
       </c>
     </row>
     <row r="568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A568" s="3" t="n">
-        <v>142550</v>
+      <c r="A568" s="3" t="s">
+        <v>567</v>
       </c>
       <c r="B568" s="0" t="n">
         <v>720</v>
       </c>
     </row>
     <row r="569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A569" s="3" t="n">
-        <v>115764</v>
+      <c r="A569" s="3" t="s">
+        <v>568</v>
       </c>
       <c r="B569" s="0" t="n">
         <v>4930</v>
       </c>
     </row>
     <row r="570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A570" s="3" t="n">
-        <v>143403</v>
+      <c r="A570" s="3" t="s">
+        <v>569</v>
       </c>
       <c r="B570" s="0" t="n">
         <v>510</v>
       </c>
     </row>
     <row r="571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A571" s="3" t="n">
-        <v>142548</v>
+      <c r="A571" s="3" t="s">
+        <v>570</v>
       </c>
       <c r="B571" s="0" t="n">
         <v>510</v>
       </c>
     </row>
     <row r="572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A572" s="3" t="n">
-        <v>138695</v>
+      <c r="A572" s="3" t="s">
+        <v>571</v>
       </c>
       <c r="B572" s="0" t="n">
         <v>1230</v>
       </c>
     </row>
     <row r="573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A573" s="3" t="n">
-        <v>134435</v>
+      <c r="A573" s="3" t="s">
+        <v>572</v>
       </c>
       <c r="B573" s="0" t="n">
         <v>340</v>
       </c>
     </row>
     <row r="574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A574" s="3" t="n">
-        <v>119764</v>
+      <c r="A574" s="3" t="s">
+        <v>573</v>
       </c>
       <c r="B574" s="0" t="n">
         <v>3660</v>
       </c>
     </row>
     <row r="575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A575" s="3" t="n">
-        <v>143396</v>
+      <c r="A575" s="3" t="s">
+        <v>574</v>
       </c>
       <c r="B575" s="0" t="n">
         <v>370</v>
       </c>
     </row>
     <row r="576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A576" s="3" t="n">
-        <v>110443</v>
+      <c r="A576" s="3" t="s">
+        <v>575</v>
       </c>
       <c r="B576" s="0" t="n">
         <v>510</v>
       </c>
     </row>
     <row r="577" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A577" s="3" t="n">
-        <v>138456</v>
+      <c r="A577" s="3" t="s">
+        <v>576</v>
       </c>
       <c r="B577" s="0" t="n">
         <v>3390</v>
       </c>
     </row>
     <row r="578" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A578" s="3" t="n">
-        <v>131058</v>
+      <c r="A578" s="3" t="s">
+        <v>577</v>
       </c>
       <c r="B578" s="0" t="n">
         <v>2270</v>
       </c>
     </row>
     <row r="579" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A579" s="3" t="n">
-        <v>122788</v>
+      <c r="A579" s="3" t="s">
+        <v>578</v>
       </c>
       <c r="B579" s="0" t="n">
         <v>870</v>
       </c>
     </row>
     <row r="580" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A580" s="3" t="n">
-        <v>122799</v>
+      <c r="A580" s="3" t="s">
+        <v>579</v>
       </c>
       <c r="B580" s="0" t="n">
         <v>510</v>
       </c>
     </row>
     <row r="581" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A581" s="3" t="n">
-        <v>142552</v>
+      <c r="A581" s="3" t="s">
+        <v>580</v>
       </c>
       <c r="B581" s="0" t="n">
         <v>510</v>
       </c>
     </row>
     <row r="582" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A582" s="3" t="n">
-        <v>134723</v>
+      <c r="A582" s="3" t="s">
+        <v>581</v>
       </c>
       <c r="B582" s="0" t="n">
         <v>3270</v>
       </c>
     </row>
     <row r="583" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A583" s="3" t="n">
-        <v>138668</v>
+      <c r="A583" s="3" t="s">
+        <v>582</v>
       </c>
       <c r="B583" s="0" t="n">
         <v>4130</v>
       </c>
     </row>
     <row r="584" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A584" s="3" t="n">
-        <v>128147</v>
+      <c r="A584" s="3" t="s">
+        <v>583</v>
       </c>
       <c r="B584" s="0" t="n">
         <v>470</v>
       </c>
     </row>
     <row r="585" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A585" s="3" t="n">
-        <v>131057</v>
+      <c r="A585" s="3" t="s">
+        <v>584</v>
       </c>
       <c r="B585" s="0" t="n">
         <v>1660</v>
       </c>
     </row>
     <row r="586" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A586" s="3" t="n">
-        <v>143364</v>
+      <c r="A586" s="3" t="s">
+        <v>585</v>
       </c>
       <c r="B586" s="0" t="n">
         <v>2060</v>
       </c>
     </row>
     <row r="587" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A587" s="3" t="n">
-        <v>143365</v>
+      <c r="A587" s="3" t="s">
+        <v>586</v>
       </c>
       <c r="B587" s="0" t="n">
         <v>2060</v>
       </c>
     </row>
     <row r="588" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A588" s="3" t="n">
-        <v>142503</v>
+      <c r="A588" s="3" t="s">
+        <v>587</v>
       </c>
       <c r="B588" s="0" t="n">
         <v>2590</v>
       </c>
     </row>
     <row r="589" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A589" s="3" t="n">
-        <v>143366</v>
+      <c r="A589" s="3" t="s">
+        <v>588</v>
       </c>
       <c r="B589" s="0" t="n">
         <v>2060</v>
       </c>
     </row>
     <row r="590" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A590" s="3" t="n">
-        <v>143367</v>
+      <c r="A590" s="3" t="s">
+        <v>589</v>
       </c>
       <c r="B590" s="0" t="n">
         <v>1790</v>
       </c>
     </row>
     <row r="591" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A591" s="3" t="n">
-        <v>143368</v>
+      <c r="A591" s="3" t="s">
+        <v>590</v>
       </c>
       <c r="B591" s="0" t="n">
         <v>2590</v>
       </c>
     </row>
     <row r="592" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A592" s="3" t="n">
-        <v>936999</v>
+      <c r="A592" s="3" t="s">
+        <v>591</v>
       </c>
       <c r="B592" s="0" t="n">
         <v>1790</v>
       </c>
     </row>
     <row r="593" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A593" s="3" t="n">
-        <v>941271</v>
+      <c r="A593" s="3" t="s">
+        <v>592</v>
       </c>
       <c r="B593" s="0" t="n">
         <v>1900</v>
       </c>
     </row>
     <row r="594" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A594" s="3" t="n">
-        <v>929368</v>
+      <c r="A594" s="3" t="s">
+        <v>593</v>
       </c>
       <c r="B594" s="0" t="n">
         <v>1650</v>
       </c>
     </row>
     <row r="595" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A595" s="3" t="n">
-        <v>937001</v>
+      <c r="A595" s="3" t="s">
+        <v>594</v>
       </c>
       <c r="B595" s="0" t="n">
         <v>1580</v>
       </c>
     </row>
     <row r="596" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A596" s="3" t="n">
-        <v>910432</v>
+      <c r="A596" s="3" t="s">
+        <v>595</v>
       </c>
       <c r="B596" s="0" t="n">
         <v>2500</v>
       </c>
     </row>
     <row r="597" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A597" s="3" t="n">
-        <v>900424</v>
+      <c r="A597" s="3" t="s">
+        <v>596</v>
       </c>
       <c r="B597" s="0" t="n">
         <v>2090</v>
       </c>
     </row>
     <row r="598" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A598" s="3" t="n">
-        <v>921318</v>
+      <c r="A598" s="3" t="s">
+        <v>597</v>
       </c>
       <c r="B598" s="0" t="n">
         <v>2500</v>
       </c>
     </row>
     <row r="599" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A599" s="3" t="n">
-        <v>910434</v>
+      <c r="A599" s="3" t="s">
+        <v>598</v>
       </c>
       <c r="B599" s="0" t="n">
         <v>2040</v>
       </c>
     </row>
     <row r="600" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A600" s="3" t="n">
-        <v>921980</v>
+      <c r="A600" s="3" t="s">
+        <v>599</v>
       </c>
       <c r="B600" s="0" t="n">
         <v>2410</v>
       </c>
     </row>
     <row r="601" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A601" s="3" t="n">
-        <v>932386</v>
+      <c r="A601" s="3" t="s">
+        <v>600</v>
       </c>
       <c r="B601" s="0" t="n">
         <v>2500</v>
       </c>
     </row>
     <row r="602" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A602" s="3" t="n">
-        <v>906163</v>
+      <c r="A602" s="3" t="s">
+        <v>601</v>
       </c>
       <c r="B602" s="0" t="n">
         <v>2350</v>
       </c>
     </row>
     <row r="603" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A603" s="3" t="n">
-        <v>921891</v>
+      <c r="A603" s="3" t="s">
+        <v>602</v>
       </c>
       <c r="B603" s="0" t="n">
         <v>2040</v>
       </c>
     </row>
     <row r="604" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A604" s="3" t="n">
-        <v>929425</v>
+      <c r="A604" s="3" t="s">
+        <v>603</v>
       </c>
       <c r="B604" s="0" t="n">
         <v>2350</v>
       </c>
     </row>
     <row r="605" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A605" s="3" t="n">
-        <v>929426</v>
+      <c r="A605" s="3" t="s">
+        <v>604</v>
       </c>
       <c r="B605" s="0" t="n">
         <v>2500</v>
       </c>
     </row>
     <row r="606" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A606" s="3" t="n">
-        <v>735691</v>
+      <c r="A606" s="3" t="s">
+        <v>605</v>
       </c>
       <c r="B606" s="0" t="n">
         <v>960</v>
       </c>
     </row>
     <row r="607" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A607" s="3" t="n">
-        <v>735692</v>
+      <c r="A607" s="3" t="s">
+        <v>606</v>
       </c>
       <c r="B607" s="0" t="n">
         <v>990</v>
       </c>
     </row>
     <row r="608" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A608" s="3" t="n">
-        <v>902642</v>
+      <c r="A608" s="3" t="s">
+        <v>607</v>
       </c>
       <c r="B608" s="0" t="n">
         <v>2240</v>
       </c>
     </row>
     <row r="609" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A609" s="3" t="n">
-        <v>926054</v>
+      <c r="A609" s="3" t="s">
+        <v>608</v>
       </c>
       <c r="B609" s="0" t="n">
         <v>1580</v>
       </c>
     </row>
     <row r="610" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A610" s="3" t="n">
-        <v>132034</v>
+      <c r="A610" s="3" t="s">
+        <v>609</v>
       </c>
       <c r="B610" s="0" t="n">
         <v>1760</v>
       </c>
     </row>
     <row r="611" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A611" s="3" t="n">
-        <v>940375</v>
+      <c r="A611" s="3" t="s">
+        <v>610</v>
       </c>
       <c r="B611" s="0" t="n">
         <v>2410</v>
       </c>
     </row>
     <row r="612" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A612" s="3" t="n">
-        <v>941205</v>
+      <c r="A612" s="3" t="s">
+        <v>611</v>
       </c>
       <c r="B612" s="0" t="n">
         <v>2350</v>
       </c>
     </row>
     <row r="613" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A613" s="3" t="n">
-        <v>925037</v>
+      <c r="A613" s="3" t="s">
+        <v>612</v>
       </c>
       <c r="B613" s="0" t="n">
         <v>850</v>
       </c>
     </row>
     <row r="614" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A614" s="3" t="n">
-        <v>973253</v>
+      <c r="A614" s="3" t="s">
+        <v>613</v>
       </c>
       <c r="B614" s="0" t="n">
         <v>850</v>
       </c>
     </row>
     <row r="615" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A615" s="3" t="n">
-        <v>143394</v>
+      <c r="A615" s="3" t="s">
+        <v>614</v>
       </c>
       <c r="B615" s="0" t="n">
         <v>510</v>
       </c>
     </row>
     <row r="616" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A616" s="3" t="n">
-        <v>138125</v>
+      <c r="A616" s="3" t="s">
+        <v>615</v>
       </c>
       <c r="B616" s="0" t="n">
         <v>940</v>
       </c>
     </row>
     <row r="617" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A617" s="3" t="n">
-        <v>142556</v>
+      <c r="A617" s="3" t="s">
+        <v>616</v>
       </c>
       <c r="B617" s="0" t="n">
         <v>480</v>
       </c>
     </row>
     <row r="618" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A618" s="3" t="n">
-        <v>130843</v>
+      <c r="A618" s="3" t="s">
+        <v>617</v>
       </c>
       <c r="B618" s="0" t="n">
         <v>870</v>
       </c>
     </row>
     <row r="619" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A619" s="3" t="n">
-        <v>134369</v>
+      <c r="A619" s="3" t="s">
+        <v>618</v>
       </c>
       <c r="B619" s="0" t="n">
         <v>870</v>
       </c>
     </row>
     <row r="620" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A620" s="3" t="n">
-        <v>130844</v>
+      <c r="A620" s="3" t="s">
+        <v>619</v>
       </c>
       <c r="B620" s="0" t="n">
         <v>700</v>
       </c>
     </row>
     <row r="621" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A621" s="3" t="n">
-        <v>142555</v>
+      <c r="A621" s="3" t="s">
+        <v>620</v>
       </c>
       <c r="B621" s="0" t="n">
         <v>480</v>
       </c>
     </row>
     <row r="622" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A622" s="3" t="n">
-        <v>142562</v>
+      <c r="A622" s="3" t="s">
+        <v>621</v>
       </c>
       <c r="B622" s="0" t="n">
         <v>1090</v>
       </c>
     </row>
     <row r="623" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A623" s="3" t="n">
-        <v>138500</v>
+      <c r="A623" s="3" t="s">
+        <v>622</v>
       </c>
       <c r="B623" s="0" t="n">
         <v>1230</v>
       </c>
     </row>
     <row r="624" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A624" s="3" t="n">
-        <v>128152</v>
+      <c r="A624" s="3" t="s">
+        <v>623</v>
       </c>
       <c r="B624" s="0" t="n">
         <v>1230</v>
       </c>
     </row>
     <row r="625" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A625" s="3" t="n">
-        <v>122832</v>
+      <c r="A625" s="3" t="s">
+        <v>624</v>
       </c>
       <c r="B625" s="0" t="n">
         <v>1230</v>
       </c>
     </row>
     <row r="626" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A626" s="3" t="n">
-        <v>119593</v>
+      <c r="A626" s="3" t="s">
+        <v>625</v>
       </c>
       <c r="B626" s="0" t="n">
         <v>1720</v>
       </c>
     </row>
     <row r="627" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A627" s="3" t="n">
-        <v>142554</v>
+      <c r="A627" s="3" t="s">
+        <v>626</v>
       </c>
       <c r="B627" s="0" t="n">
         <v>440</v>
       </c>
     </row>
     <row r="628" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A628" s="3" t="n">
-        <v>138697</v>
+      <c r="A628" s="3" t="s">
+        <v>627</v>
       </c>
       <c r="B628" s="0" t="n">
         <v>1880</v>
       </c>
     </row>
     <row r="629" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A629" s="3" t="n">
-        <v>131056</v>
+      <c r="A629" s="3" t="s">
+        <v>628</v>
       </c>
       <c r="B629" s="0" t="n">
         <v>1990</v>
       </c>
     </row>
     <row r="630" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A630" s="3" t="n">
-        <v>68772</v>
+      <c r="A630" s="3" t="s">
+        <v>629</v>
       </c>
       <c r="B630" s="0" t="n">
         <v>3320</v>
       </c>
     </row>
     <row r="631" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A631" s="3" t="n">
-        <v>123990</v>
+      <c r="A631" s="3" t="s">
+        <v>630</v>
       </c>
       <c r="B631" s="0" t="n">
         <v>2810</v>
       </c>
     </row>
     <row r="632" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A632" s="3" t="n">
-        <v>123991</v>
+      <c r="A632" s="3" t="s">
+        <v>631</v>
       </c>
       <c r="B632" s="0" t="n">
         <v>1910</v>
       </c>
     </row>
     <row r="633" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A633" s="3" t="n">
-        <v>134180</v>
+      <c r="A633" s="3" t="s">
+        <v>632</v>
       </c>
       <c r="B633" s="0" t="n">
         <v>3410</v>
       </c>
     </row>
     <row r="634" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A634" s="3" t="n">
-        <v>110660</v>
+      <c r="A634" s="3" t="s">
+        <v>633</v>
       </c>
       <c r="B634" s="0" t="n">
         <v>2410</v>
       </c>
     </row>
     <row r="635" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A635" s="3" t="n">
-        <v>75032</v>
+      <c r="A635" s="3" t="s">
+        <v>634</v>
       </c>
       <c r="B635" s="0" t="n">
         <v>2410</v>
       </c>
     </row>
     <row r="636" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A636" s="3" t="n">
-        <v>75036</v>
+      <c r="A636" s="3" t="s">
+        <v>635</v>
       </c>
       <c r="B636" s="0" t="n">
         <v>2370</v>
       </c>
     </row>
     <row r="637" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A637" s="3" t="n">
-        <v>134178</v>
+      <c r="A637" s="3" t="s">
+        <v>636</v>
       </c>
       <c r="B637" s="0" t="n">
         <v>1930</v>
       </c>
     </row>
     <row r="638" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A638" s="3" t="n">
-        <v>138505</v>
+      <c r="A638" s="3" t="s">
+        <v>637</v>
       </c>
       <c r="B638" s="0" t="n">
         <v>2540</v>
       </c>
     </row>
     <row r="639" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A639" s="3" t="n">
-        <v>942042</v>
+      <c r="A639" s="3" t="s">
+        <v>638</v>
       </c>
       <c r="B639" s="0" t="n">
         <v>1200</v>
       </c>
     </row>
     <row r="640" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A640" s="3" t="n">
-        <v>942043</v>
+      <c r="A640" s="3" t="s">
+        <v>639</v>
       </c>
       <c r="B640" s="0" t="n">
         <v>1300</v>
       </c>
     </row>
     <row r="641" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A641" s="3" t="n">
-        <v>942437</v>
+      <c r="A641" s="3" t="s">
+        <v>640</v>
       </c>
       <c r="B641" s="0" t="n">
         <v>1090</v>
       </c>
     </row>
     <row r="642" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A642" s="3" t="n">
-        <v>942440</v>
+      <c r="A642" s="3" t="s">
+        <v>641</v>
       </c>
       <c r="B642" s="0" t="n">
         <v>1230</v>
       </c>
     </row>
     <row r="643" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A643" s="3" t="n">
-        <v>942441</v>
+      <c r="A643" s="3" t="s">
+        <v>642</v>
       </c>
       <c r="B643" s="0" t="n">
         <v>980</v>
       </c>
     </row>
     <row r="644" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A644" s="3" t="n">
-        <v>114586</v>
+      <c r="A644" s="3" t="s">
+        <v>643</v>
       </c>
       <c r="B644" s="0" t="n">
         <v>590</v>
       </c>
     </row>
     <row r="645" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A645" s="3" t="n">
-        <v>143471</v>
+      <c r="A645" s="3" t="s">
+        <v>644</v>
       </c>
       <c r="B645" s="0" t="n">
         <v>590</v>
       </c>
     </row>
     <row r="646" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A646" s="3" t="n">
-        <v>143474</v>
+      <c r="A646" s="3" t="s">
+        <v>645</v>
       </c>
       <c r="B646" s="0" t="n">
         <v>840</v>
       </c>
     </row>
     <row r="647" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A647" s="3" t="n">
-        <v>96514</v>
+      <c r="A647" s="3" t="s">
+        <v>646</v>
       </c>
       <c r="B647" s="0" t="n">
         <v>620</v>
       </c>
     </row>
     <row r="648" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A648" s="3" t="n">
-        <v>78731</v>
+      <c r="A648" s="3" t="s">
+        <v>647</v>
       </c>
       <c r="B648" s="0" t="n">
         <v>840</v>
       </c>
     </row>
     <row r="649" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A649" s="3" t="n">
-        <v>143470</v>
+      <c r="A649" s="3" t="s">
+        <v>648</v>
       </c>
       <c r="B649" s="0" t="n">
         <v>590</v>
       </c>
     </row>
     <row r="650" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A650" s="3" t="n">
-        <v>78732</v>
+      <c r="A650" s="3" t="s">
+        <v>649</v>
       </c>
       <c r="B650" s="0" t="n">
         <v>840</v>
       </c>
     </row>
     <row r="651" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A651" s="3" t="n">
-        <v>143472</v>
+      <c r="A651" s="3" t="s">
+        <v>650</v>
       </c>
       <c r="B651" s="0" t="n">
         <v>840</v>
       </c>
     </row>
     <row r="652" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A652" s="3" t="n">
-        <v>143473</v>
+      <c r="A652" s="3" t="s">
+        <v>651</v>
       </c>
       <c r="B652" s="0" t="n">
         <v>840</v>
       </c>
     </row>
     <row r="653" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A653" s="3" t="n">
-        <v>111113</v>
+      <c r="A653" s="3" t="s">
+        <v>652</v>
       </c>
       <c r="B653" s="0" t="n">
         <v>590</v>
       </c>
     </row>
     <row r="654" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A654" s="3" t="n">
-        <v>107321</v>
+      <c r="A654" s="3" t="s">
+        <v>653</v>
       </c>
       <c r="B654" s="0" t="n">
         <v>480</v>
       </c>
     </row>
     <row r="655" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A655" s="3" t="n">
-        <v>107322</v>
+      <c r="A655" s="3" t="s">
+        <v>654</v>
       </c>
       <c r="B655" s="0" t="n">
         <v>590</v>
       </c>
     </row>
     <row r="656" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A656" s="3" t="n">
-        <v>138131</v>
+      <c r="A656" s="3" t="s">
+        <v>655</v>
       </c>
       <c r="B656" s="0" t="n">
         <v>1990</v>
       </c>
     </row>
     <row r="657" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A657" s="3" t="n">
-        <v>138133</v>
+      <c r="A657" s="3" t="s">
+        <v>656</v>
       </c>
       <c r="B657" s="0" t="n">
         <v>680</v>
       </c>
     </row>
     <row r="658" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A658" s="3" t="n">
-        <v>138134</v>
+      <c r="A658" s="3" t="s">
+        <v>657</v>
       </c>
       <c r="B658" s="0" t="n">
         <v>1380</v>
       </c>
     </row>
     <row r="659" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A659" s="3" t="n">
-        <v>138135</v>
+      <c r="A659" s="3" t="s">
+        <v>658</v>
       </c>
       <c r="B659" s="0" t="n">
         <v>1380</v>
       </c>
     </row>
     <row r="660" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A660" s="3" t="n">
-        <v>115770</v>
+      <c r="A660" s="3" t="s">
+        <v>659</v>
       </c>
       <c r="B660" s="0" t="n">
         <v>650</v>
       </c>
     </row>
     <row r="661" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A661" s="3" t="n">
-        <v>115771</v>
+      <c r="A661" s="3" t="s">
+        <v>660</v>
       </c>
       <c r="B661" s="0" t="n">
         <v>650</v>
       </c>
     </row>
     <row r="662" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A662" s="3" t="n">
-        <v>143466</v>
+      <c r="A662" s="3" t="s">
+        <v>661</v>
       </c>
       <c r="B662" s="0" t="n">
         <v>650</v>
       </c>
     </row>
     <row r="663" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A663" s="3" t="n">
-        <v>115773</v>
+      <c r="A663" s="3" t="s">
+        <v>662</v>
       </c>
       <c r="B663" s="0" t="n">
         <v>700</v>
       </c>
     </row>
     <row r="664" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A664" s="3" t="n">
-        <v>130997</v>
+      <c r="A664" s="3" t="s">
+        <v>663</v>
       </c>
       <c r="B664" s="0" t="n">
         <v>650</v>
       </c>
     </row>
     <row r="665" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A665" s="3" t="n">
-        <v>143467</v>
+      <c r="A665" s="3" t="s">
+        <v>664</v>
       </c>
       <c r="B665" s="0" t="n">
         <v>1340</v>
       </c>
     </row>
     <row r="666" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A666" s="3" t="n">
-        <v>128121</v>
+      <c r="A666" s="3" t="s">
+        <v>665</v>
       </c>
       <c r="B666" s="0" t="n">
         <v>590</v>
       </c>
     </row>
     <row r="667" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A667" s="3" t="n">
-        <v>128125</v>
+      <c r="A667" s="3" t="s">
+        <v>666</v>
       </c>
       <c r="B667" s="0" t="n">
         <v>590</v>
       </c>
     </row>
     <row r="668" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A668" s="3" t="n">
-        <v>841725</v>
+      <c r="A668" s="3" t="s">
+        <v>667</v>
       </c>
       <c r="B668" s="0" t="n">
         <v>330</v>
       </c>
     </row>
     <row r="669" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A669" s="3" t="n">
-        <v>136669</v>
+      <c r="A669" s="3" t="s">
+        <v>668</v>
       </c>
       <c r="B669" s="0" t="n">
         <v>660</v>
       </c>
     </row>
     <row r="670" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A670" s="3" t="n">
-        <v>126732</v>
+      <c r="A670" s="3" t="s">
+        <v>669</v>
       </c>
       <c r="B670" s="0" t="n">
         <v>520</v>
       </c>
     </row>
     <row r="671" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A671" s="3" t="n">
-        <v>941828</v>
+      <c r="A671" s="3" t="s">
+        <v>670</v>
       </c>
       <c r="B671" s="0" t="n">
         <v>260</v>
       </c>
     </row>
     <row r="672" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A672" s="3" t="n">
-        <v>133442</v>
+      <c r="A672" s="3" t="s">
+        <v>671</v>
       </c>
       <c r="B672" s="0" t="n">
         <v>470</v>
       </c>
     </row>
     <row r="673" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A673" s="3" t="n">
-        <v>841724</v>
+      <c r="A673" s="3" t="s">
+        <v>672</v>
       </c>
       <c r="B673" s="0" t="n">
         <v>410</v>
       </c>
     </row>
     <row r="674" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A674" s="3" t="n">
-        <v>841726</v>
+      <c r="A674" s="3" t="s">
+        <v>673</v>
       </c>
       <c r="B674" s="0" t="n">
         <v>520</v>
       </c>
     </row>
     <row r="675" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A675" s="3" t="n">
-        <v>933265</v>
+      <c r="A675" s="3" t="s">
+        <v>674</v>
       </c>
       <c r="B675" s="0" t="n">
         <v>260</v>
       </c>
     </row>
     <row r="676" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A676" s="3" t="n">
-        <v>135651</v>
+      <c r="A676" s="3" t="s">
+        <v>675</v>
       </c>
       <c r="B676" s="0" t="n">
         <v>480</v>
       </c>
     </row>
     <row r="677" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A677" s="3" t="n">
-        <v>841660</v>
+      <c r="A677" s="3" t="s">
+        <v>676</v>
       </c>
       <c r="B677" s="0" t="n">
         <v>340</v>
       </c>
     </row>
     <row r="678" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A678" s="3" t="n">
-        <v>903990</v>
+      <c r="A678" s="3" t="s">
+        <v>677</v>
       </c>
       <c r="B678" s="0" t="n">
         <v>90</v>
       </c>
     </row>
     <row r="679" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A679" s="3" t="n">
-        <v>841707</v>
+      <c r="A679" s="3" t="s">
+        <v>678</v>
       </c>
       <c r="B679" s="0" t="n">
         <v>520</v>
       </c>
     </row>
     <row r="680" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A680" s="3" t="n">
-        <v>933432</v>
+      <c r="A680" s="3" t="s">
+        <v>679</v>
       </c>
       <c r="B680" s="0" t="n">
         <v>470</v>
       </c>
     </row>
     <row r="681" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A681" s="3" t="n">
-        <v>943369</v>
+      <c r="A681" s="3" t="s">
+        <v>522</v>
       </c>
       <c r="B681" s="0" t="n">
         <v>650</v>
       </c>
     </row>
     <row r="682" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A682" s="3" t="n">
-        <v>942515</v>
+      <c r="A682" s="3" t="s">
+        <v>523</v>
       </c>
       <c r="B682" s="0" t="n">
         <v>970</v>
       </c>
     </row>
     <row r="683" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A683" s="3" t="n">
-        <v>135701</v>
+      <c r="A683" s="3" t="s">
+        <v>680</v>
       </c>
       <c r="B683" s="0" t="n">
         <v>730</v>
       </c>
     </row>
     <row r="684" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A684" s="3" t="n">
-        <v>135702</v>
+      <c r="A684" s="3" t="s">
+        <v>681</v>
       </c>
       <c r="B684" s="0" t="n">
         <v>510</v>
       </c>
     </row>
     <row r="685" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A685" s="3" t="n">
-        <v>135703</v>
+      <c r="A685" s="3" t="s">
+        <v>682</v>
       </c>
       <c r="B685" s="0" t="n">
         <v>370</v>
       </c>
     </row>
     <row r="686" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A686" s="3" t="n">
-        <v>113296</v>
+      <c r="A686" s="3" t="s">
+        <v>683</v>
       </c>
       <c r="B686" s="0" t="n">
         <v>470</v>
       </c>
     </row>
     <row r="687" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A687" s="3" t="n">
-        <v>835704</v>
+      <c r="A687" s="3" t="s">
+        <v>684</v>
       </c>
       <c r="B687" s="0" t="n">
         <v>1550</v>
       </c>
     </row>
     <row r="688" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A688" s="3" t="n">
-        <v>135705</v>
+      <c r="A688" s="3" t="s">
+        <v>685</v>
       </c>
       <c r="B688" s="0" t="n">
         <v>1380</v>
       </c>
     </row>
     <row r="689" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A689" s="3" t="n">
-        <v>121718</v>
+      <c r="A689" s="3" t="s">
+        <v>686</v>
       </c>
       <c r="B689" s="0" t="n">
         <v>390</v>
       </c>
     </row>
     <row r="690" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A690" s="3" t="n">
-        <v>114562</v>
+      <c r="A690" s="3" t="s">
+        <v>687</v>
       </c>
       <c r="B690" s="0" t="n">
         <v>1190</v>
       </c>
     </row>
     <row r="691" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A691" s="3" t="n">
-        <v>135722</v>
+      <c r="A691" s="3" t="s">
+        <v>688</v>
       </c>
       <c r="B691" s="0" t="n">
         <v>520</v>
       </c>
     </row>
     <row r="692" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A692" s="3" t="n">
-        <v>135723</v>
+      <c r="A692" s="3" t="s">
+        <v>689</v>
       </c>
       <c r="B692" s="0" t="n">
         <v>1440</v>
       </c>
     </row>
     <row r="693" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A693" s="3" t="n">
-        <v>135724</v>
+      <c r="A693" s="3" t="s">
+        <v>690</v>
       </c>
       <c r="B693" s="0" t="n">
         <v>840</v>
       </c>
     </row>
     <row r="694" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A694" s="3" t="n">
-        <v>123946</v>
+      <c r="A694" s="3" t="s">
+        <v>691</v>
       </c>
       <c r="B694" s="0" t="n">
         <v>910</v>
       </c>
     </row>
     <row r="695" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A695" s="3" t="n">
-        <v>841829</v>
+      <c r="A695" s="3" t="s">
+        <v>692</v>
       </c>
       <c r="B695" s="0" t="n">
         <v>110</v>
       </c>
     </row>
     <row r="696" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A696" s="3" t="n">
-        <v>133434</v>
+      <c r="A696" s="3" t="s">
+        <v>693</v>
       </c>
       <c r="B696" s="0" t="n">
         <v>440</v>
       </c>
     </row>
     <row r="697" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A697" s="3" t="n">
-        <v>841714</v>
+      <c r="A697" s="3" t="s">
+        <v>694</v>
       </c>
       <c r="B697" s="0" t="n">
         <v>520</v>
       </c>
     </row>
     <row r="698" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A698" s="3" t="n">
-        <v>835659</v>
+      <c r="A698" s="3" t="s">
+        <v>695</v>
       </c>
       <c r="B698" s="0" t="n">
         <v>970</v>
       </c>
     </row>
     <row r="699" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A699" s="3" t="n">
-        <v>135661</v>
+      <c r="A699" s="3" t="s">
+        <v>696</v>
       </c>
       <c r="B699" s="0" t="n">
         <v>480</v>
       </c>
     </row>
     <row r="700" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A700" s="3" t="n">
-        <v>121722</v>
+      <c r="A700" s="3" t="s">
+        <v>697</v>
       </c>
       <c r="B700" s="0" t="n">
         <v>510</v>
       </c>
     </row>
     <row r="701" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A701" s="3" t="n">
-        <v>118851</v>
+      <c r="A701" s="3" t="s">
+        <v>698</v>
       </c>
       <c r="B701" s="0" t="n">
         <v>1190</v>
       </c>
     </row>
     <row r="702" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A702" s="3" t="n">
-        <v>114561</v>
+      <c r="A702" s="3" t="s">
+        <v>699</v>
       </c>
       <c r="B702" s="0" t="n">
         <v>1190</v>
       </c>
     </row>
     <row r="703" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A703" s="3" t="n">
-        <v>942507</v>
+      <c r="A703" s="3" t="s">
+        <v>518</v>
       </c>
       <c r="B703" s="0" t="n">
         <v>650</v>
       </c>
     </row>
     <row r="704" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A704" s="3" t="n">
-        <v>118846</v>
+      <c r="A704" s="3" t="s">
+        <v>700</v>
       </c>
       <c r="B704" s="0" t="n">
         <v>460</v>
       </c>
     </row>
     <row r="705" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A705" s="3" t="n">
-        <v>941287</v>
+      <c r="A705" s="3" t="s">
+        <v>701</v>
       </c>
       <c r="B705" s="0" t="n">
         <v>620</v>
       </c>
     </row>
     <row r="706" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A706" s="3" t="n">
-        <v>127898</v>
+      <c r="A706" s="3" t="s">
+        <v>702</v>
       </c>
       <c r="B706" s="0" t="n">
         <v>520</v>
       </c>
     </row>
     <row r="707" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A707" s="3" t="n">
-        <v>942229</v>
+      <c r="A707" s="3" t="s">
+        <v>703</v>
       </c>
       <c r="B707" s="0" t="n">
         <v>1440</v>
       </c>
     </row>
     <row r="708" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A708" s="3" t="n">
-        <v>935989</v>
+      <c r="A708" s="3" t="s">
+        <v>704</v>
       </c>
       <c r="B708" s="0" t="n">
         <v>820</v>
       </c>
     </row>
     <row r="709" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A709" s="3" t="n">
-        <v>942378</v>
+      <c r="A709" s="3" t="s">
+        <v>705</v>
       </c>
       <c r="B709" s="0" t="n">
         <v>2030</v>
       </c>
     </row>
     <row r="710" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A710" s="3" t="n">
-        <v>942379</v>
+      <c r="A710" s="3" t="s">
+        <v>706</v>
       </c>
       <c r="B710" s="0" t="n">
         <v>1080</v>
       </c>
     </row>
     <row r="711" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A711" s="3" t="n">
-        <v>128211</v>
+      <c r="A711" s="3" t="s">
+        <v>707</v>
       </c>
       <c r="B711" s="0" t="n">
         <v>410</v>
       </c>
     </row>
     <row r="712" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A712" s="3" t="n">
-        <v>123936</v>
+      <c r="A712" s="3" t="s">
+        <v>708</v>
       </c>
       <c r="B712" s="0" t="n">
         <v>380</v>
       </c>
     </row>
     <row r="713" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A713" s="3" t="n">
-        <v>123943</v>
+      <c r="A713" s="3" t="s">
+        <v>709</v>
       </c>
       <c r="B713" s="0" t="n">
         <v>980</v>
       </c>
     </row>
     <row r="714" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A714" s="3" t="n">
-        <v>128209</v>
+      <c r="A714" s="3" t="s">
+        <v>710</v>
       </c>
       <c r="B714" s="0" t="n">
         <v>390</v>
       </c>
     </row>
     <row r="715" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A715" s="3" t="n">
-        <v>143490</v>
+      <c r="A715" s="3" t="s">
+        <v>155</v>
       </c>
       <c r="B715" s="0" t="n">
         <v>2830</v>
